--- a/research/traditional_assets/database/data/greece/greece_green_renewable_energy.xlsx
+++ b/research/traditional_assets/database/data/greece/greece_green_renewable_energy.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09015090716365159</v>
+        <v>0.08998767516789156</v>
       </c>
       <c r="C2">
-        <v>3824.160003853804</v>
+        <v>3801.247686625934</v>
       </c>
       <c r="D2">
-        <v>3824.160003853804</v>
+        <v>3838.286686625935</v>
       </c>
       <c r="E2">
-        <v>-1274.1</v>
+        <v>-1237.061</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>37.039</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -1451,28 +1451,28 @@
         <v>231.925</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>1.8630617</v>
       </c>
       <c r="N2">
-        <v>231.925</v>
+        <v>230.0619383</v>
       </c>
       <c r="O2">
-        <v>51.02349999999999</v>
+        <v>50.61362642599999</v>
       </c>
       <c r="P2">
-        <v>180.9015</v>
+        <v>179.448311874</v>
       </c>
       <c r="Q2">
-        <v>241.1015</v>
+        <v>239.6483118739999</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09015090716365159</v>
+        <v>0.09050033855342582</v>
       </c>
       <c r="T2">
-        <v>0.5780409979533054</v>
+        <v>0.5825952603614224</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>124.4859469764206</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08998767516789156</v>
+        <v>0.08982444317213152</v>
       </c>
       <c r="C3">
-        <v>3801.247686625934</v>
+        <v>3778.440126049426</v>
       </c>
       <c r="D3">
-        <v>3838.286686625935</v>
+        <v>3852.518126049426</v>
       </c>
       <c r="E3">
-        <v>-1237.061</v>
+        <v>-1200.022</v>
       </c>
       <c r="F3">
-        <v>37.039</v>
+        <v>74.078</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -1533,28 +1533,28 @@
         <v>231.925</v>
       </c>
       <c r="M3">
-        <v>1.8630617</v>
+        <v>3.7261234</v>
       </c>
       <c r="N3">
-        <v>230.0619383</v>
+        <v>228.1988765999999</v>
       </c>
       <c r="O3">
-        <v>50.61362642599999</v>
+        <v>50.20375285199999</v>
       </c>
       <c r="P3">
-        <v>179.448311874</v>
+        <v>177.995123748</v>
       </c>
       <c r="Q3">
-        <v>239.6483118739999</v>
+        <v>238.195123748</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09050033855342582</v>
+        <v>0.09085690119605258</v>
       </c>
       <c r="T3">
-        <v>0.5825952603614224</v>
+        <v>0.5872424669003172</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>124.4859469764206</v>
+        <v>62.24297348821028</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08982444317213152</v>
+        <v>0.08966121117637149</v>
       </c>
       <c r="C4">
-        <v>3778.440126049426</v>
+        <v>3755.738491697813</v>
       </c>
       <c r="D4">
-        <v>3852.518126049426</v>
+        <v>3866.855491697813</v>
       </c>
       <c r="E4">
-        <v>-1200.022</v>
+        <v>-1162.983</v>
       </c>
       <c r="F4">
-        <v>74.078</v>
+        <v>111.117</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -1615,28 +1615,28 @@
         <v>231.925</v>
       </c>
       <c r="M4">
-        <v>3.7261234</v>
+        <v>5.5891851</v>
       </c>
       <c r="N4">
-        <v>228.1988765999999</v>
+        <v>226.3358148999999</v>
       </c>
       <c r="O4">
-        <v>50.20375285199999</v>
+        <v>49.79387927799999</v>
       </c>
       <c r="P4">
-        <v>177.995123748</v>
+        <v>176.541935622</v>
       </c>
       <c r="Q4">
-        <v>238.195123748</v>
+        <v>236.7419356219999</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09085690119605258</v>
+        <v>0.0912208156457438</v>
       </c>
       <c r="T4">
-        <v>0.5872424669003172</v>
+        <v>0.5919854921307357</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>62.24297348821028</v>
+        <v>41.49531565880685</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08966121117637149</v>
+        <v>0.08949797918061145</v>
       </c>
       <c r="C5">
-        <v>3755.738491697813</v>
+        <v>3733.143970620206</v>
       </c>
       <c r="D5">
-        <v>3866.855491697813</v>
+        <v>3881.299970620206</v>
       </c>
       <c r="E5">
-        <v>-1162.983</v>
+        <v>-1125.944</v>
       </c>
       <c r="F5">
-        <v>111.117</v>
+        <v>148.156</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -1697,28 +1697,28 @@
         <v>231.925</v>
       </c>
       <c r="M5">
-        <v>5.5891851</v>
+        <v>7.4522468</v>
       </c>
       <c r="N5">
-        <v>226.3358148999999</v>
+        <v>224.4727531999999</v>
       </c>
       <c r="O5">
-        <v>49.79387927799999</v>
+        <v>49.38400570399999</v>
       </c>
       <c r="P5">
-        <v>176.541935622</v>
+        <v>175.0887474959999</v>
       </c>
       <c r="Q5">
-        <v>236.7419356219999</v>
+        <v>235.2887474959999</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.0912208156457438</v>
+        <v>0.09159231164647026</v>
       </c>
       <c r="T5">
-        <v>0.5919854921307357</v>
+        <v>0.5968273303867878</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>41.49531565880685</v>
+        <v>31.12148674410514</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08949797918061145</v>
+        <v>0.08933474718485142</v>
       </c>
       <c r="C6">
-        <v>3733.143970620206</v>
+        <v>3710.657767668908</v>
       </c>
       <c r="D6">
-        <v>3881.299970620206</v>
+        <v>3895.852767668908</v>
       </c>
       <c r="E6">
-        <v>-1125.944</v>
+        <v>-1088.905</v>
       </c>
       <c r="F6">
-        <v>148.156</v>
+        <v>185.195</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1779,28 +1779,28 @@
         <v>231.925</v>
       </c>
       <c r="M6">
-        <v>7.4522468</v>
+        <v>9.3153085</v>
       </c>
       <c r="N6">
-        <v>224.4727531999999</v>
+        <v>222.6096914999999</v>
       </c>
       <c r="O6">
-        <v>49.38400570399999</v>
+        <v>48.97413212999999</v>
       </c>
       <c r="P6">
-        <v>175.0887474959999</v>
+        <v>173.63555937</v>
       </c>
       <c r="Q6">
-        <v>235.2887474959999</v>
+        <v>233.8355593699999</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09159231164647026</v>
+        <v>0.09197162861563307</v>
       </c>
       <c r="T6">
-        <v>0.5968273303867878</v>
+        <v>0.6017711020798096</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>31.12148674410514</v>
+        <v>24.89718939528411</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08933474718485142</v>
+        <v>0.08917151518909139</v>
       </c>
       <c r="C7">
-        <v>3710.657767668908</v>
+        <v>3688.281105834437</v>
       </c>
       <c r="D7">
-        <v>3895.852767668908</v>
+        <v>3910.515105834437</v>
       </c>
       <c r="E7">
-        <v>-1088.905</v>
+        <v>-1051.866</v>
       </c>
       <c r="F7">
-        <v>185.195</v>
+        <v>222.234</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1861,28 +1861,28 @@
         <v>231.925</v>
       </c>
       <c r="M7">
-        <v>9.3153085</v>
+        <v>11.1783702</v>
       </c>
       <c r="N7">
-        <v>222.6096914999999</v>
+        <v>220.7466298</v>
       </c>
       <c r="O7">
-        <v>48.97413212999999</v>
+        <v>48.56425855599999</v>
       </c>
       <c r="P7">
-        <v>173.63555937</v>
+        <v>172.182371244</v>
       </c>
       <c r="Q7">
-        <v>233.8355593699999</v>
+        <v>232.382371244</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09197162861563307</v>
+        <v>0.09235901615860787</v>
       </c>
       <c r="T7">
-        <v>0.6017711020798096</v>
+        <v>0.6068200604045977</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>24.89718939528411</v>
+        <v>20.74765782940343</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08917151518909139</v>
+        <v>0.08900828319333134</v>
       </c>
       <c r="C8">
-        <v>3688.281105834437</v>
+        <v>3666.015226588137</v>
       </c>
       <c r="D8">
-        <v>3910.515105834437</v>
+        <v>3925.288226588137</v>
       </c>
       <c r="E8">
-        <v>-1051.866</v>
+        <v>-1014.827</v>
       </c>
       <c r="F8">
-        <v>222.234</v>
+        <v>259.273</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1943,28 +1943,28 @@
         <v>231.925</v>
       </c>
       <c r="M8">
-        <v>11.1783702</v>
+        <v>13.0414319</v>
       </c>
       <c r="N8">
-        <v>220.7466298</v>
+        <v>218.8835681</v>
       </c>
       <c r="O8">
-        <v>48.56425855599999</v>
+        <v>48.15438498199999</v>
       </c>
       <c r="P8">
-        <v>172.182371244</v>
+        <v>170.729183118</v>
       </c>
       <c r="Q8">
-        <v>232.382371244</v>
+        <v>230.929183118</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09235901615860787</v>
+        <v>0.09275473461648533</v>
       </c>
       <c r="T8">
-        <v>0.6068200604045977</v>
+        <v>0.6119775984783059</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>20.74765782940343</v>
+        <v>17.78370671091723</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08900828319333137</v>
+        <v>0.08884505119757131</v>
       </c>
       <c r="C9">
-        <v>3666.015226588134</v>
+        <v>3643.861390232581</v>
       </c>
       <c r="D9">
-        <v>3925.288226588134</v>
+        <v>3940.173390232581</v>
       </c>
       <c r="E9">
-        <v>-1014.827</v>
+        <v>-977.7879999999999</v>
       </c>
       <c r="F9">
-        <v>259.273</v>
+        <v>296.312</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -2025,28 +2025,28 @@
         <v>231.925</v>
       </c>
       <c r="M9">
-        <v>13.0414319</v>
+        <v>14.9044936</v>
       </c>
       <c r="N9">
-        <v>218.8835681</v>
+        <v>217.0205064</v>
       </c>
       <c r="O9">
-        <v>48.15438498199999</v>
+        <v>47.74451140799999</v>
       </c>
       <c r="P9">
-        <v>170.729183118</v>
+        <v>169.275994992</v>
       </c>
       <c r="Q9">
-        <v>230.929183118</v>
+        <v>229.475994992</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09275473461648534</v>
+        <v>0.09315905564953404</v>
       </c>
       <c r="T9">
-        <v>0.611977598478306</v>
+        <v>0.6172472569449209</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>17.78370671091722</v>
+        <v>15.56074337205257</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08884505119757131</v>
+        <v>0.08868181920181128</v>
       </c>
       <c r="C10">
-        <v>3643.861390232581</v>
+        <v>3621.820876259989</v>
       </c>
       <c r="D10">
-        <v>3940.173390232581</v>
+        <v>3955.171876259989</v>
       </c>
       <c r="E10">
-        <v>-977.7879999999999</v>
+        <v>-940.7489999999999</v>
       </c>
       <c r="F10">
-        <v>296.312</v>
+        <v>333.351</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -2107,28 +2107,28 @@
         <v>231.925</v>
       </c>
       <c r="M10">
-        <v>14.9044936</v>
+        <v>16.7675553</v>
       </c>
       <c r="N10">
-        <v>217.0205064</v>
+        <v>215.1574447</v>
       </c>
       <c r="O10">
-        <v>47.74451140799999</v>
+        <v>47.33463783399999</v>
       </c>
       <c r="P10">
-        <v>169.275994992</v>
+        <v>167.822806866</v>
       </c>
       <c r="Q10">
-        <v>229.475994992</v>
+        <v>228.0228068659999</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09315905564953404</v>
+        <v>0.09357226285913328</v>
       </c>
       <c r="T10">
-        <v>0.6172472569449209</v>
+        <v>0.6226327320811319</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>15.56074337205257</v>
+        <v>13.83177188626895</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08868181920181128</v>
+        <v>0.08863558720605126</v>
       </c>
       <c r="C11">
-        <v>3621.820876259989</v>
+        <v>3589.050651391607</v>
       </c>
       <c r="D11">
-        <v>3955.171876259989</v>
+        <v>3959.440651391607</v>
       </c>
       <c r="E11">
-        <v>-940.7489999999999</v>
+        <v>-903.7099999999999</v>
       </c>
       <c r="F11">
-        <v>333.351</v>
+        <v>370.39</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -2189,45 +2189,45 @@
         <v>231.925</v>
       </c>
       <c r="M11">
-        <v>16.7675553</v>
+        <v>19.186202</v>
       </c>
       <c r="N11">
-        <v>215.1574447</v>
+        <v>212.7387979999999</v>
       </c>
       <c r="O11">
-        <v>47.33463783399999</v>
+        <v>46.80253555999999</v>
       </c>
       <c r="P11">
-        <v>167.822806866</v>
+        <v>165.93626244</v>
       </c>
       <c r="Q11">
-        <v>228.0228068659999</v>
+        <v>226.1362624399999</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09357226285913328</v>
+        <v>0.09399465245116806</v>
       </c>
       <c r="T11">
-        <v>0.6226327320811319</v>
+        <v>0.6281378844425919</v>
       </c>
       <c r="U11">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V11">
         <v>0.22</v>
       </c>
       <c r="W11">
-        <v>0.039234</v>
+        <v>0.040404</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y11">
-        <v>13.83177188626895</v>
+        <v>12.08811415620455</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08863558720605126</v>
+        <v>0.08848405521029122</v>
       </c>
       <c r="C12">
-        <v>3589.050651391607</v>
+        <v>3566.067999623819</v>
       </c>
       <c r="D12">
-        <v>3959.440651391607</v>
+        <v>3973.496999623819</v>
       </c>
       <c r="E12">
-        <v>-903.7099999999998</v>
+        <v>-866.6709999999998</v>
       </c>
       <c r="F12">
-        <v>370.39</v>
+        <v>407.429</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -2271,28 +2271,28 @@
         <v>231.925</v>
       </c>
       <c r="M12">
-        <v>19.186202</v>
+        <v>21.1048222</v>
       </c>
       <c r="N12">
-        <v>212.7387979999999</v>
+        <v>210.8201778</v>
       </c>
       <c r="O12">
-        <v>46.80253555999999</v>
+        <v>46.38043911599999</v>
       </c>
       <c r="P12">
-        <v>165.93626244</v>
+        <v>164.439738684</v>
       </c>
       <c r="Q12">
-        <v>226.1362624399999</v>
+        <v>224.639738684</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09399465245116806</v>
+        <v>0.09442653394414745</v>
       </c>
       <c r="T12">
-        <v>0.6281378844425919</v>
+        <v>0.6337667480930737</v>
       </c>
       <c r="U12">
         <v>0.0518</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>12.08811415620454</v>
+        <v>10.98919468745868</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08848405521029122</v>
+        <v>0.08833252321453119</v>
       </c>
       <c r="C13">
-        <v>3566.067999623819</v>
+        <v>3543.185505868756</v>
       </c>
       <c r="D13">
-        <v>3973.496999623819</v>
+        <v>3987.653505868756</v>
       </c>
       <c r="E13">
-        <v>-866.6709999999998</v>
+        <v>-829.6319999999998</v>
       </c>
       <c r="F13">
-        <v>407.429</v>
+        <v>444.468</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -2353,28 +2353,28 @@
         <v>231.925</v>
       </c>
       <c r="M13">
-        <v>21.1048222</v>
+        <v>23.0234424</v>
       </c>
       <c r="N13">
-        <v>210.8201778</v>
+        <v>208.9015576</v>
       </c>
       <c r="O13">
-        <v>46.38043911599999</v>
+        <v>45.95834267199999</v>
       </c>
       <c r="P13">
-        <v>164.439738684</v>
+        <v>162.943214928</v>
       </c>
       <c r="Q13">
-        <v>224.639738684</v>
+        <v>223.143214928</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09442653394414745</v>
+        <v>0.09486823092560362</v>
       </c>
       <c r="T13">
-        <v>0.6337667480930737</v>
+        <v>0.6395235404628843</v>
       </c>
       <c r="U13">
         <v>0.0518</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>10.98919468745868</v>
+        <v>10.07342846350379</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08833252321453119</v>
+        <v>0.08835337121877114</v>
       </c>
       <c r="C14">
-        <v>3543.185505868756</v>
+        <v>3504.192850616147</v>
       </c>
       <c r="D14">
-        <v>3987.653505868756</v>
+        <v>3985.699850616147</v>
       </c>
       <c r="E14">
-        <v>-829.6319999999998</v>
+        <v>-792.5929999999998</v>
       </c>
       <c r="F14">
-        <v>444.468</v>
+        <v>481.507</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -2435,45 +2435,45 @@
         <v>231.925</v>
       </c>
       <c r="M14">
-        <v>23.0234424</v>
+        <v>25.7606245</v>
       </c>
       <c r="N14">
-        <v>208.9015576</v>
+        <v>206.1643754999999</v>
       </c>
       <c r="O14">
-        <v>45.95834267199999</v>
+        <v>45.35616260999999</v>
       </c>
       <c r="P14">
-        <v>162.943214928</v>
+        <v>160.80821289</v>
       </c>
       <c r="Q14">
-        <v>223.143214928</v>
+        <v>221.00821289</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09486823092560362</v>
+        <v>0.09532008186065649</v>
       </c>
       <c r="T14">
-        <v>0.6395235404628843</v>
+        <v>0.6454126728871734</v>
       </c>
       <c r="U14">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V14">
         <v>0.22</v>
       </c>
       <c r="W14">
-        <v>0.040404</v>
+        <v>0.04173</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y14">
-        <v>10.07342846350379</v>
+        <v>9.003081427626103</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08835337121877114</v>
+        <v>0.08821509922301113</v>
       </c>
       <c r="C15">
-        <v>3504.192850616147</v>
+        <v>3480.14711676289</v>
       </c>
       <c r="D15">
-        <v>3985.699850616147</v>
+        <v>3998.69311676289</v>
       </c>
       <c r="E15">
-        <v>-792.5929999999998</v>
+        <v>-755.5539999999999</v>
       </c>
       <c r="F15">
-        <v>481.507</v>
+        <v>518.546</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -2517,28 +2517,28 @@
         <v>231.925</v>
       </c>
       <c r="M15">
-        <v>25.7606245</v>
+        <v>27.742211</v>
       </c>
       <c r="N15">
-        <v>206.1643754999999</v>
+        <v>204.182789</v>
       </c>
       <c r="O15">
-        <v>45.35616260999999</v>
+        <v>44.92021357999999</v>
       </c>
       <c r="P15">
-        <v>160.80821289</v>
+        <v>159.26257542</v>
       </c>
       <c r="Q15">
-        <v>221.00821289</v>
+        <v>219.46257542</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09532008186065649</v>
+        <v>0.09578244095698968</v>
       </c>
       <c r="T15">
-        <v>0.6454126728871734</v>
+        <v>0.6514387618794694</v>
       </c>
       <c r="U15">
         <v>0.0535</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>9.003081427626103</v>
+        <v>8.360004182795667</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08821509922301113</v>
+        <v>0.0880768272272511</v>
       </c>
       <c r="C16">
-        <v>3480.14711676289</v>
+        <v>3456.186375325545</v>
       </c>
       <c r="D16">
-        <v>3998.69311676289</v>
+        <v>4011.771375325545</v>
       </c>
       <c r="E16">
-        <v>-755.5539999999999</v>
+        <v>-718.5149999999998</v>
       </c>
       <c r="F16">
-        <v>518.546</v>
+        <v>555.5850000000002</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -2599,28 +2599,28 @@
         <v>231.925</v>
       </c>
       <c r="M16">
-        <v>27.742211</v>
+        <v>29.72379750000001</v>
       </c>
       <c r="N16">
-        <v>204.182789</v>
+        <v>202.2012024999999</v>
       </c>
       <c r="O16">
-        <v>44.92021357999999</v>
+        <v>44.48426454999998</v>
       </c>
       <c r="P16">
-        <v>159.26257542</v>
+        <v>157.71693795</v>
       </c>
       <c r="Q16">
-        <v>219.46257542</v>
+        <v>217.9169379499999</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09578244095698968</v>
+        <v>0.09625567909088364</v>
       </c>
       <c r="T16">
-        <v>0.6514387618794694</v>
+        <v>0.6576066412009958</v>
       </c>
       <c r="U16">
         <v>0.0535</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>8.360004182795667</v>
+        <v>7.802670570609287</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.0880768272272511</v>
+        <v>0.08803839523149105</v>
       </c>
       <c r="C17">
-        <v>3456.186375325545</v>
+        <v>3422.797617709087</v>
       </c>
       <c r="D17">
-        <v>4011.771375325545</v>
+        <v>4015.421617709087</v>
       </c>
       <c r="E17">
-        <v>-718.5149999999999</v>
+        <v>-681.4759999999999</v>
       </c>
       <c r="F17">
-        <v>555.585</v>
+        <v>592.624</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -2681,45 +2681,45 @@
         <v>231.925</v>
       </c>
       <c r="M17">
-        <v>29.7237975</v>
+        <v>32.1794832</v>
       </c>
       <c r="N17">
-        <v>202.2012025</v>
+        <v>199.7455168</v>
       </c>
       <c r="O17">
-        <v>44.48426454999999</v>
+        <v>43.94401369599999</v>
       </c>
       <c r="P17">
-        <v>157.71693795</v>
+        <v>155.801503104</v>
       </c>
       <c r="Q17">
-        <v>217.91693795</v>
+        <v>216.001503104</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09625567909088364</v>
+        <v>0.09674018479939411</v>
       </c>
       <c r="T17">
-        <v>0.6576066412009958</v>
+        <v>0.6639213747920822</v>
       </c>
       <c r="U17">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V17">
         <v>0.22</v>
       </c>
       <c r="W17">
-        <v>0.04173</v>
+        <v>0.042354</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y17">
-        <v>7.80267057060929</v>
+        <v>7.207231966981992</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08803839523149105</v>
+        <v>0.08790636323573102</v>
       </c>
       <c r="C18">
-        <v>3422.797617709087</v>
+        <v>3398.349686831727</v>
       </c>
       <c r="D18">
-        <v>4015.421617709087</v>
+        <v>4028.012686831727</v>
       </c>
       <c r="E18">
-        <v>-681.4759999999999</v>
+        <v>-644.4369999999999</v>
       </c>
       <c r="F18">
-        <v>592.624</v>
+        <v>629.663</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -2763,28 +2763,28 @@
         <v>231.925</v>
       </c>
       <c r="M18">
-        <v>32.1794832</v>
+        <v>34.1907009</v>
       </c>
       <c r="N18">
-        <v>199.7455168</v>
+        <v>197.7342991</v>
       </c>
       <c r="O18">
-        <v>43.94401369599999</v>
+        <v>43.50154580199999</v>
       </c>
       <c r="P18">
-        <v>155.801503104</v>
+        <v>154.232753298</v>
       </c>
       <c r="Q18">
-        <v>216.001503104</v>
+        <v>214.432753298</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09674018479939411</v>
+        <v>0.09723636534425424</v>
       </c>
       <c r="T18">
-        <v>0.6639213747920822</v>
+        <v>0.6703882706383757</v>
       </c>
       <c r="U18">
         <v>0.0543</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>7.207231966981992</v>
+        <v>6.783277145394815</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08790636323573102</v>
+        <v>0.08777433123997098</v>
       </c>
       <c r="C19">
-        <v>3398.349686831727</v>
+        <v>3373.980967412224</v>
       </c>
       <c r="D19">
-        <v>4028.012686831727</v>
+        <v>4040.682967412224</v>
       </c>
       <c r="E19">
-        <v>-644.4369999999999</v>
+        <v>-607.3979999999998</v>
       </c>
       <c r="F19">
-        <v>629.663</v>
+        <v>666.7020000000001</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -2845,28 +2845,28 @@
         <v>231.925</v>
       </c>
       <c r="M19">
-        <v>34.1907009</v>
+        <v>36.20191860000001</v>
       </c>
       <c r="N19">
-        <v>197.7342991</v>
+        <v>195.7230814</v>
       </c>
       <c r="O19">
-        <v>43.50154580199999</v>
+        <v>43.05907790799999</v>
       </c>
       <c r="P19">
-        <v>154.232753298</v>
+        <v>152.6640034919999</v>
       </c>
       <c r="Q19">
-        <v>214.432753298</v>
+        <v>212.8640034919999</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09723636534425424</v>
+        <v>0.09774464785362316</v>
       </c>
       <c r="T19">
-        <v>0.6703882706383757</v>
+        <v>0.677012895651652</v>
       </c>
       <c r="U19">
         <v>0.0543</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>6.783277145394815</v>
+        <v>6.406428415095103</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08777433123997098</v>
+        <v>0.08779049924421096</v>
       </c>
       <c r="C20">
-        <v>3373.980967412224</v>
+        <v>3335.386144535016</v>
       </c>
       <c r="D20">
-        <v>4040.682967412224</v>
+        <v>4039.127144535016</v>
       </c>
       <c r="E20">
-        <v>-607.3979999999999</v>
+        <v>-570.3589999999999</v>
       </c>
       <c r="F20">
-        <v>666.702</v>
+        <v>703.741</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -2927,45 +2927,45 @@
         <v>231.925</v>
       </c>
       <c r="M20">
-        <v>36.2019186</v>
+        <v>38.9168773</v>
       </c>
       <c r="N20">
-        <v>195.7230814</v>
+        <v>193.0081226999999</v>
       </c>
       <c r="O20">
-        <v>43.05907790799999</v>
+        <v>42.46178699399999</v>
       </c>
       <c r="P20">
-        <v>152.6640034919999</v>
+        <v>150.546335706</v>
       </c>
       <c r="Q20">
-        <v>212.8640034919999</v>
+        <v>210.7463357059999</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09774464785362315</v>
+        <v>0.09826548054840858</v>
       </c>
       <c r="T20">
-        <v>0.6770128956516518</v>
+        <v>0.6838010916529103</v>
       </c>
       <c r="U20">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V20">
         <v>0.22</v>
       </c>
       <c r="W20">
-        <v>0.042354</v>
+        <v>0.04313400000000001</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y20">
-        <v>6.406428415095104</v>
+        <v>5.959496652625824</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08779049924421096</v>
+        <v>0.08766626724845093</v>
       </c>
       <c r="C21">
-        <v>3335.386144535016</v>
+        <v>3310.332660781694</v>
       </c>
       <c r="D21">
-        <v>4039.127144535016</v>
+        <v>4051.112660781695</v>
       </c>
       <c r="E21">
-        <v>-570.3589999999999</v>
+        <v>-533.3199999999998</v>
       </c>
       <c r="F21">
-        <v>703.741</v>
+        <v>740.7800000000001</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -3009,28 +3009,28 @@
         <v>231.925</v>
       </c>
       <c r="M21">
-        <v>38.9168773</v>
+        <v>40.96513400000001</v>
       </c>
       <c r="N21">
-        <v>193.0081226999999</v>
+        <v>190.9598659999999</v>
       </c>
       <c r="O21">
-        <v>42.46178699399999</v>
+        <v>42.01117051999999</v>
       </c>
       <c r="P21">
-        <v>150.546335706</v>
+        <v>148.94869548</v>
       </c>
       <c r="Q21">
-        <v>210.7463357059999</v>
+        <v>209.14869548</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09826548054840858</v>
+        <v>0.09879933406056365</v>
       </c>
       <c r="T21">
-        <v>0.6838010916529103</v>
+        <v>0.6907589925542</v>
       </c>
       <c r="U21">
         <v>0.0553</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>5.959496652625824</v>
+        <v>5.661521819994533</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08766626724845093</v>
+        <v>0.0875420352526909</v>
       </c>
       <c r="C22">
-        <v>3310.332660781694</v>
+        <v>3285.350519242261</v>
       </c>
       <c r="D22">
-        <v>4051.112660781695</v>
+        <v>4063.169519242261</v>
       </c>
       <c r="E22">
-        <v>-533.3199999999998</v>
+        <v>-496.2809999999998</v>
       </c>
       <c r="F22">
-        <v>740.7800000000001</v>
+        <v>777.8190000000001</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -3091,28 +3091,28 @@
         <v>231.925</v>
       </c>
       <c r="M22">
-        <v>40.96513400000001</v>
+        <v>43.0133907</v>
       </c>
       <c r="N22">
-        <v>190.9598659999999</v>
+        <v>188.9116093</v>
       </c>
       <c r="O22">
-        <v>42.01117051999999</v>
+        <v>41.56055404599999</v>
       </c>
       <c r="P22">
-        <v>148.94869548</v>
+        <v>147.351055254</v>
       </c>
       <c r="Q22">
-        <v>209.14869548</v>
+        <v>207.5510552539999</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09879933406056365</v>
+        <v>0.09934670285150746</v>
       </c>
       <c r="T22">
-        <v>0.6907589925542</v>
+        <v>0.6978930428453959</v>
       </c>
       <c r="U22">
         <v>0.0553</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>5.661521819994533</v>
+        <v>5.391925542851936</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08754203525269089</v>
+        <v>0.08741780325693085</v>
       </c>
       <c r="C23">
-        <v>3285.350519242262</v>
+        <v>3260.440358800913</v>
       </c>
       <c r="D23">
-        <v>4063.169519242262</v>
+        <v>4075.298358800913</v>
       </c>
       <c r="E23">
-        <v>-496.2809999999999</v>
+        <v>-459.2419999999998</v>
       </c>
       <c r="F23">
-        <v>777.819</v>
+        <v>814.8580000000001</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -3173,28 +3173,28 @@
         <v>231.925</v>
       </c>
       <c r="M23">
-        <v>43.0133907</v>
+        <v>45.06164740000001</v>
       </c>
       <c r="N23">
-        <v>188.9116093</v>
+        <v>186.8633526</v>
       </c>
       <c r="O23">
-        <v>41.56055404599999</v>
+        <v>41.10993757199999</v>
       </c>
       <c r="P23">
-        <v>147.351055254</v>
+        <v>145.7534150279999</v>
       </c>
       <c r="Q23">
-        <v>207.5510552539999</v>
+        <v>205.9534150279999</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09934670285150744</v>
+        <v>0.09990810673965494</v>
       </c>
       <c r="T23">
-        <v>0.6978930428453958</v>
+        <v>0.7052100175030326</v>
       </c>
       <c r="U23">
         <v>0.0553</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>5.391925542851936</v>
+        <v>5.146838018176848</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08741780325693085</v>
+        <v>0.08729357126117082</v>
       </c>
       <c r="C24">
-        <v>3260.440358800913</v>
+        <v>3235.602825993138</v>
       </c>
       <c r="D24">
-        <v>4075.298358800913</v>
+        <v>4087.499825993138</v>
       </c>
       <c r="E24">
-        <v>-459.2419999999998</v>
+        <v>-422.2029999999999</v>
       </c>
       <c r="F24">
-        <v>814.8580000000001</v>
+        <v>851.897</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -3255,28 +3255,28 @@
         <v>231.925</v>
       </c>
       <c r="M24">
-        <v>45.06164740000001</v>
+        <v>47.1099041</v>
       </c>
       <c r="N24">
-        <v>186.8633526</v>
+        <v>184.8150959</v>
       </c>
       <c r="O24">
-        <v>41.10993757199999</v>
+        <v>40.65932109799999</v>
       </c>
       <c r="P24">
-        <v>145.7534150279999</v>
+        <v>144.155774802</v>
       </c>
       <c r="Q24">
-        <v>205.9534150279999</v>
+        <v>204.355774802</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09990810673965494</v>
+        <v>0.1004840925469751</v>
       </c>
       <c r="T24">
-        <v>0.7052100175030326</v>
+        <v>0.7127170434504783</v>
       </c>
       <c r="U24">
         <v>0.0553</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>5.146838018176848</v>
+        <v>4.92306245216916</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08729357126117082</v>
+        <v>0.08716933926541079</v>
       </c>
       <c r="C25">
-        <v>3235.602825993138</v>
+        <v>3210.838575120603</v>
       </c>
       <c r="D25">
-        <v>4087.499825993138</v>
+        <v>4099.774575120603</v>
       </c>
       <c r="E25">
-        <v>-422.2029999999999</v>
+        <v>-385.1639999999999</v>
       </c>
       <c r="F25">
-        <v>851.897</v>
+        <v>888.936</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -3337,28 +3337,28 @@
         <v>231.925</v>
       </c>
       <c r="M25">
-        <v>47.1099041</v>
+        <v>49.1581608</v>
       </c>
       <c r="N25">
-        <v>184.8150959</v>
+        <v>182.7668391999999</v>
       </c>
       <c r="O25">
-        <v>40.65932109799999</v>
+        <v>40.20870462399999</v>
       </c>
       <c r="P25">
-        <v>144.155774802</v>
+        <v>142.558134576</v>
       </c>
       <c r="Q25">
-        <v>204.355774802</v>
+        <v>202.7581345759999</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1004840925469751</v>
+        <v>0.1010752358755405</v>
       </c>
       <c r="T25">
-        <v>0.7127170434504783</v>
+        <v>0.7204216227123301</v>
       </c>
       <c r="U25">
         <v>0.0553</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>4.92306245216916</v>
+        <v>4.717934849995444</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08716933926541079</v>
+        <v>0.08704510726965076</v>
       </c>
       <c r="C26">
-        <v>3210.838575120603</v>
+        <v>3186.14826836811</v>
       </c>
       <c r="D26">
-        <v>4099.774575120603</v>
+        <v>4112.12326836811</v>
       </c>
       <c r="E26">
-        <v>-385.1639999999999</v>
+        <v>-348.1249999999999</v>
       </c>
       <c r="F26">
-        <v>888.936</v>
+        <v>925.975</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -3419,28 +3419,28 @@
         <v>231.925</v>
       </c>
       <c r="M26">
-        <v>49.1581608</v>
+        <v>51.2064175</v>
       </c>
       <c r="N26">
-        <v>182.7668391999999</v>
+        <v>180.7185825</v>
       </c>
       <c r="O26">
-        <v>40.20870462399999</v>
+        <v>39.75808814999999</v>
       </c>
       <c r="P26">
-        <v>142.558134576</v>
+        <v>140.96049435</v>
       </c>
       <c r="Q26">
-        <v>202.7581345759999</v>
+        <v>201.16049435</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1010752358755405</v>
+        <v>0.101682143026201</v>
       </c>
       <c r="T26">
-        <v>0.7204216227123301</v>
+        <v>0.7283316574211649</v>
       </c>
       <c r="U26">
         <v>0.0553</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>4.717934849995444</v>
+        <v>4.529217455995627</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08704510726965076</v>
+        <v>0.08742787527389072</v>
       </c>
       <c r="C27">
-        <v>3186.14826836811</v>
+        <v>3111.298325429853</v>
       </c>
       <c r="D27">
-        <v>4112.12326836811</v>
+        <v>4074.312325429853</v>
       </c>
       <c r="E27">
-        <v>-348.1249999999999</v>
+        <v>-311.0859999999999</v>
       </c>
       <c r="F27">
-        <v>925.975</v>
+        <v>963.014</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -3501,45 +3501,45 @@
         <v>231.925</v>
       </c>
       <c r="M27">
-        <v>51.2064175</v>
+        <v>55.66220920000001</v>
       </c>
       <c r="N27">
-        <v>180.7185825</v>
+        <v>176.2627907999999</v>
       </c>
       <c r="O27">
-        <v>39.75808814999999</v>
+        <v>38.77781397599999</v>
       </c>
       <c r="P27">
-        <v>140.96049435</v>
+        <v>137.4849768239999</v>
       </c>
       <c r="Q27">
-        <v>201.16049435</v>
+        <v>197.6849768239999</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.101682143026201</v>
+        <v>0.1023054530728253</v>
       </c>
       <c r="T27">
-        <v>0.7283316574211649</v>
+        <v>0.73645547685186</v>
       </c>
       <c r="U27">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V27">
         <v>0.22</v>
       </c>
       <c r="W27">
-        <v>0.04313400000000001</v>
+        <v>0.04508400000000001</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y27">
-        <v>4.529217455995627</v>
+        <v>4.166651006730072</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08742787527389072</v>
+        <v>0.08732314327813069</v>
       </c>
       <c r="C28">
-        <v>3111.298325429853</v>
+        <v>3084.535783990173</v>
       </c>
       <c r="D28">
-        <v>4074.312325429853</v>
+        <v>4084.588783990173</v>
       </c>
       <c r="E28">
-        <v>-311.0859999999999</v>
+        <v>-274.0469999999998</v>
       </c>
       <c r="F28">
-        <v>963.014</v>
+        <v>1000.053</v>
       </c>
       <c r="G28">
         <v>0</v>
@@ -3583,28 +3583,28 @@
         <v>231.925</v>
       </c>
       <c r="M28">
-        <v>55.66220920000001</v>
+        <v>57.80306340000001</v>
       </c>
       <c r="N28">
-        <v>176.2627907999999</v>
+        <v>174.1219365999999</v>
       </c>
       <c r="O28">
-        <v>38.77781397599999</v>
+        <v>38.30682605199998</v>
       </c>
       <c r="P28">
-        <v>137.4849768239999</v>
+        <v>135.815110548</v>
       </c>
       <c r="Q28">
-        <v>197.6849768239999</v>
+        <v>196.0151105479999</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1023054530728253</v>
+        <v>0.1029458401070283</v>
       </c>
       <c r="T28">
-        <v>0.73645547685186</v>
+        <v>0.7448018666779166</v>
       </c>
       <c r="U28">
         <v>0.0578</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>4.166651006730072</v>
+        <v>4.012330599073403</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08732314327813069</v>
+        <v>0.08798281128237065</v>
       </c>
       <c r="C29">
-        <v>3084.535783990173</v>
+        <v>2983.620706285466</v>
       </c>
       <c r="D29">
-        <v>4084.588783990173</v>
+        <v>4020.712706285466</v>
       </c>
       <c r="E29">
-        <v>-274.0469999999998</v>
+        <v>-237.0079999999998</v>
       </c>
       <c r="F29">
-        <v>1000.053</v>
+        <v>1037.092</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -3665,45 +3665,45 @@
         <v>231.925</v>
       </c>
       <c r="M29">
-        <v>57.80306340000001</v>
+        <v>63.5737396</v>
       </c>
       <c r="N29">
-        <v>174.1219365999999</v>
+        <v>168.3512603999999</v>
       </c>
       <c r="O29">
-        <v>38.30682605199998</v>
+        <v>37.03727728799999</v>
       </c>
       <c r="P29">
-        <v>135.815110548</v>
+        <v>131.313983112</v>
       </c>
       <c r="Q29">
-        <v>196.0151105479999</v>
+        <v>191.5139831119999</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1029458401070283</v>
+        <v>0.1036040156699592</v>
       </c>
       <c r="T29">
-        <v>0.7448018666779166</v>
+        <v>0.7533801006658082</v>
       </c>
       <c r="U29">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V29">
         <v>0.22</v>
       </c>
       <c r="W29">
-        <v>0.04508400000000001</v>
+        <v>0.047814</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y29">
-        <v>4.012330599073403</v>
+        <v>3.648125805706102</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08798281128237065</v>
+        <v>0.08790537928661062</v>
       </c>
       <c r="C30">
-        <v>2983.620706285466</v>
+        <v>2953.975816361192</v>
       </c>
       <c r="D30">
-        <v>4020.712706285466</v>
+        <v>4028.106816361193</v>
       </c>
       <c r="E30">
-        <v>-237.0079999999998</v>
+        <v>-199.9689999999998</v>
       </c>
       <c r="F30">
-        <v>1037.092</v>
+        <v>1074.131</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -3747,28 +3747,28 @@
         <v>231.925</v>
       </c>
       <c r="M30">
-        <v>63.5737396</v>
+        <v>65.84423030000001</v>
       </c>
       <c r="N30">
-        <v>168.3512603999999</v>
+        <v>166.0807697</v>
       </c>
       <c r="O30">
-        <v>37.03727728799999</v>
+        <v>36.53776933399999</v>
       </c>
       <c r="P30">
-        <v>131.313983112</v>
+        <v>129.543000366</v>
       </c>
       <c r="Q30">
-        <v>191.5139831119999</v>
+        <v>189.743000366</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1036040156699592</v>
+        <v>0.1042807313895924</v>
       </c>
       <c r="T30">
-        <v>0.7533801006658082</v>
+        <v>0.7621999750477247</v>
       </c>
       <c r="U30">
         <v>0.0613</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>3.648125805706102</v>
+        <v>3.52232836413003</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08790537928661062</v>
+        <v>0.08848314729085058</v>
       </c>
       <c r="C31">
-        <v>2953.975816361193</v>
+        <v>2862.411520457034</v>
       </c>
       <c r="D31">
-        <v>4028.106816361193</v>
+        <v>3973.581520457034</v>
       </c>
       <c r="E31">
-        <v>-199.9690000000001</v>
+        <v>-162.9299999999998</v>
       </c>
       <c r="F31">
-        <v>1074.131</v>
+        <v>1111.17</v>
       </c>
       <c r="G31">
         <v>0</v>
@@ -3829,45 +3829,45 @@
         <v>231.925</v>
       </c>
       <c r="M31">
-        <v>65.84423029999999</v>
+        <v>71.22599700000001</v>
       </c>
       <c r="N31">
-        <v>166.0807697</v>
+        <v>160.6990029999999</v>
       </c>
       <c r="O31">
-        <v>36.53776933399999</v>
+        <v>35.35378065999999</v>
       </c>
       <c r="P31">
-        <v>129.543000366</v>
+        <v>125.34522234</v>
       </c>
       <c r="Q31">
-        <v>189.743000366</v>
+        <v>185.54522234</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1042807313895924</v>
+        <v>0.1049767818440723</v>
       </c>
       <c r="T31">
-        <v>0.7621999750477247</v>
+        <v>0.7712718458405533</v>
       </c>
       <c r="U31">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V31">
         <v>0.22</v>
       </c>
       <c r="W31">
-        <v>0.047814</v>
+        <v>0.04999800000000001</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y31">
-        <v>3.52232836413003</v>
+        <v>3.256184676502316</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08848314729085058</v>
+        <v>0.08842755529509055</v>
       </c>
       <c r="C32">
-        <v>2862.411520457034</v>
+        <v>2830.554598704501</v>
       </c>
       <c r="D32">
-        <v>3973.581520457034</v>
+        <v>3978.763598704501</v>
       </c>
       <c r="E32">
-        <v>-162.9299999999998</v>
+        <v>-125.8909999999998</v>
       </c>
       <c r="F32">
-        <v>1111.17</v>
+        <v>1148.209</v>
       </c>
       <c r="G32">
         <v>0</v>
@@ -3911,28 +3911,28 @@
         <v>231.925</v>
       </c>
       <c r="M32">
-        <v>71.22599700000001</v>
+        <v>73.60019690000001</v>
       </c>
       <c r="N32">
-        <v>160.6990029999999</v>
+        <v>158.3248030999999</v>
       </c>
       <c r="O32">
-        <v>35.35378065999999</v>
+        <v>34.83145668199999</v>
       </c>
       <c r="P32">
-        <v>125.34522234</v>
+        <v>123.493346418</v>
       </c>
       <c r="Q32">
-        <v>185.54522234</v>
+        <v>183.6933464179999</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1049767818440723</v>
+        <v>0.1056930076740443</v>
       </c>
       <c r="T32">
-        <v>0.7712718458405533</v>
+        <v>0.7806066694099856</v>
       </c>
       <c r="U32">
         <v>0.0641</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>3.256184676502316</v>
+        <v>3.151146461131273</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08842755529509055</v>
+        <v>0.08837196329933052</v>
       </c>
       <c r="C33">
-        <v>2830.554598704501</v>
+        <v>2798.711210839045</v>
       </c>
       <c r="D33">
-        <v>3978.763598704501</v>
+        <v>3983.959210839045</v>
       </c>
       <c r="E33">
-        <v>-125.8909999999998</v>
+        <v>-88.85199999999986</v>
       </c>
       <c r="F33">
-        <v>1148.209</v>
+        <v>1185.248</v>
       </c>
       <c r="G33">
         <v>0</v>
@@ -3993,28 +3993,28 @@
         <v>231.925</v>
       </c>
       <c r="M33">
-        <v>73.60019690000001</v>
+        <v>75.97439680000001</v>
       </c>
       <c r="N33">
-        <v>158.3248030999999</v>
+        <v>155.9506031999999</v>
       </c>
       <c r="O33">
-        <v>34.83145668199999</v>
+        <v>34.30913270399999</v>
       </c>
       <c r="P33">
-        <v>123.493346418</v>
+        <v>121.641470496</v>
       </c>
       <c r="Q33">
-        <v>183.6933464179999</v>
+        <v>181.8414704959999</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1056930076740443</v>
+        <v>0.1064302989696037</v>
       </c>
       <c r="T33">
-        <v>0.7806066694099856</v>
+        <v>0.790216046613813</v>
       </c>
       <c r="U33">
         <v>0.0641</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>3.151146461131273</v>
+        <v>3.052673134220921</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08837196329933052</v>
+        <v>0.09032409130357048</v>
       </c>
       <c r="C34">
-        <v>2798.711210839045</v>
+        <v>2586.998273302559</v>
       </c>
       <c r="D34">
-        <v>3983.959210839045</v>
+        <v>3809.285273302559</v>
       </c>
       <c r="E34">
-        <v>-88.85199999999986</v>
+        <v>-51.81299999999987</v>
       </c>
       <c r="F34">
-        <v>1185.248</v>
+        <v>1222.287</v>
       </c>
       <c r="G34">
         <v>0</v>
@@ -4075,45 +4075,45 @@
         <v>231.925</v>
       </c>
       <c r="M34">
-        <v>75.97439680000001</v>
+        <v>87.88243530000001</v>
       </c>
       <c r="N34">
-        <v>155.9506031999999</v>
+        <v>144.0425647</v>
       </c>
       <c r="O34">
-        <v>34.30913270399999</v>
+        <v>31.68936423399999</v>
       </c>
       <c r="P34">
-        <v>121.641470496</v>
+        <v>112.353200466</v>
       </c>
       <c r="Q34">
-        <v>181.8414704959999</v>
+        <v>172.553200466</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1064302989696037</v>
+        <v>0.107189598960553</v>
       </c>
       <c r="T34">
-        <v>0.790216046613813</v>
+        <v>0.8001122708983515</v>
       </c>
       <c r="U34">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V34">
         <v>0.22</v>
       </c>
       <c r="W34">
-        <v>0.04999800000000001</v>
+        <v>0.05608200000000001</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y34">
-        <v>3.052673134220921</v>
+        <v>2.639037018128695</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09032409130357048</v>
+        <v>0.09032933930781045</v>
       </c>
       <c r="C35">
-        <v>2586.998273302559</v>
+        <v>2549.510330075997</v>
       </c>
       <c r="D35">
-        <v>3809.285273302559</v>
+        <v>3808.836330075997</v>
       </c>
       <c r="E35">
-        <v>-51.81299999999987</v>
+        <v>-14.77399999999989</v>
       </c>
       <c r="F35">
-        <v>1222.287</v>
+        <v>1259.326</v>
       </c>
       <c r="G35">
         <v>0</v>
@@ -4157,28 +4157,28 @@
         <v>231.925</v>
       </c>
       <c r="M35">
-        <v>87.88243530000001</v>
+        <v>90.54553940000001</v>
       </c>
       <c r="N35">
-        <v>144.0425647</v>
+        <v>141.3794606</v>
       </c>
       <c r="O35">
-        <v>31.68936423399999</v>
+        <v>31.10348133199999</v>
       </c>
       <c r="P35">
-        <v>112.353200466</v>
+        <v>110.275979268</v>
       </c>
       <c r="Q35">
-        <v>172.553200466</v>
+        <v>170.4759792679999</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.107189598960553</v>
+        <v>0.107971908042137</v>
       </c>
       <c r="T35">
-        <v>0.8001122708983515</v>
+        <v>0.81030838076727</v>
       </c>
       <c r="U35">
         <v>0.07190000000000001</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>2.639037018128695</v>
+        <v>2.56141828230138</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09032933930781045</v>
+        <v>0.09139928731205042</v>
       </c>
       <c r="C36">
-        <v>2549.510330075997</v>
+        <v>2423.100265963673</v>
       </c>
       <c r="D36">
-        <v>3808.836330075997</v>
+        <v>3719.465265963674</v>
       </c>
       <c r="E36">
-        <v>-14.77399999999989</v>
+        <v>22.26500000000033</v>
       </c>
       <c r="F36">
-        <v>1259.326</v>
+        <v>1296.365</v>
       </c>
       <c r="G36">
         <v>0</v>
@@ -4239,45 +4239,45 @@
         <v>231.925</v>
       </c>
       <c r="M36">
-        <v>90.54553940000001</v>
+        <v>98.26446700000002</v>
       </c>
       <c r="N36">
-        <v>141.3794606</v>
+        <v>133.6605329999999</v>
       </c>
       <c r="O36">
-        <v>31.10348133199999</v>
+        <v>29.40531725999999</v>
       </c>
       <c r="P36">
-        <v>110.275979268</v>
+        <v>104.2552157399999</v>
       </c>
       <c r="Q36">
-        <v>170.4759792679999</v>
+        <v>164.4552157399999</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.107971908042137</v>
+        <v>0.1087782881723853</v>
       </c>
       <c r="T36">
-        <v>0.81030838076727</v>
+        <v>0.8208182170936938</v>
       </c>
       <c r="U36">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V36">
         <v>0.22</v>
       </c>
       <c r="W36">
-        <v>0.05608200000000001</v>
+        <v>0.05912400000000001</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y36">
-        <v>2.56141828230138</v>
+        <v>2.360212262689013</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09139928731205042</v>
+        <v>0.09143495531629038</v>
       </c>
       <c r="C37">
-        <v>2423.100265963673</v>
+        <v>2383.154154475182</v>
       </c>
       <c r="D37">
-        <v>3719.465265963674</v>
+        <v>3716.558154475182</v>
       </c>
       <c r="E37">
-        <v>22.26500000000033</v>
+        <v>59.30400000000031</v>
       </c>
       <c r="F37">
-        <v>1296.365</v>
+        <v>1333.404</v>
       </c>
       <c r="G37">
         <v>0</v>
@@ -4321,28 +4321,28 @@
         <v>231.925</v>
       </c>
       <c r="M37">
-        <v>98.26446700000002</v>
+        <v>101.0720232</v>
       </c>
       <c r="N37">
-        <v>133.6605329999999</v>
+        <v>130.8529767999999</v>
       </c>
       <c r="O37">
-        <v>29.40531725999999</v>
+        <v>28.78765489599998</v>
       </c>
       <c r="P37">
-        <v>104.2552157399999</v>
+        <v>102.0653219039999</v>
       </c>
       <c r="Q37">
-        <v>164.4552157399999</v>
+        <v>162.2653219039999</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1087782881723853</v>
+        <v>0.1096098676817037</v>
       </c>
       <c r="T37">
-        <v>0.8208182170936938</v>
+        <v>0.8316564858053183</v>
       </c>
       <c r="U37">
         <v>0.07580000000000001</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>2.360212262689013</v>
+        <v>2.294650810947652</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09143495531629039</v>
+        <v>0.09147062332053034</v>
       </c>
       <c r="C38">
-        <v>2383.154154475181</v>
+        <v>2343.212583799028</v>
       </c>
       <c r="D38">
-        <v>3716.558154475181</v>
+        <v>3713.655583799028</v>
       </c>
       <c r="E38">
-        <v>59.30400000000009</v>
+        <v>96.34300000000007</v>
       </c>
       <c r="F38">
-        <v>1333.404</v>
+        <v>1370.443</v>
       </c>
       <c r="G38">
         <v>0</v>
@@ -4403,28 +4403,28 @@
         <v>231.925</v>
       </c>
       <c r="M38">
-        <v>101.0720232</v>
+        <v>103.8795794</v>
       </c>
       <c r="N38">
-        <v>130.8529768</v>
+        <v>128.0454205999999</v>
       </c>
       <c r="O38">
-        <v>28.78765489599999</v>
+        <v>28.16999253199999</v>
       </c>
       <c r="P38">
-        <v>102.065321904</v>
+        <v>99.87542806799996</v>
       </c>
       <c r="Q38">
-        <v>162.265321904</v>
+        <v>160.075428068</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1096098676817037</v>
+        <v>0.1104678465405244</v>
       </c>
       <c r="T38">
-        <v>0.8316564858053181</v>
+        <v>0.8428388265395339</v>
       </c>
       <c r="U38">
         <v>0.07580000000000001</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>2.294650810947653</v>
+        <v>2.232633221462581</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09147062332053034</v>
+        <v>0.09150629132477033</v>
       </c>
       <c r="C39">
-        <v>2343.212583799028</v>
+        <v>2303.275543304611</v>
       </c>
       <c r="D39">
-        <v>3713.655583799028</v>
+        <v>3710.757543304611</v>
       </c>
       <c r="E39">
-        <v>96.34300000000007</v>
+        <v>133.3820000000001</v>
       </c>
       <c r="F39">
-        <v>1370.443</v>
+        <v>1407.482</v>
       </c>
       <c r="G39">
         <v>0</v>
@@ -4485,28 +4485,28 @@
         <v>231.925</v>
       </c>
       <c r="M39">
-        <v>103.8795794</v>
+        <v>106.6871356</v>
       </c>
       <c r="N39">
-        <v>128.0454205999999</v>
+        <v>125.2378643999999</v>
       </c>
       <c r="O39">
-        <v>28.16999253199999</v>
+        <v>27.55233016799999</v>
       </c>
       <c r="P39">
-        <v>99.87542806799996</v>
+        <v>97.68553423199995</v>
       </c>
       <c r="Q39">
-        <v>160.075428068</v>
+        <v>157.8855342319999</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1104678465405244</v>
+        <v>0.1113535021367263</v>
       </c>
       <c r="T39">
-        <v>0.8428388265395339</v>
+        <v>0.8543818879425953</v>
       </c>
       <c r="U39">
         <v>0.07580000000000001</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>2.232633221462581</v>
+        <v>2.173879715634618</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09150629132477033</v>
+        <v>0.09154195932901028</v>
       </c>
       <c r="C40">
-        <v>2303.275543304611</v>
+        <v>2263.343022394497</v>
       </c>
       <c r="D40">
-        <v>3710.757543304611</v>
+        <v>3707.864022394497</v>
       </c>
       <c r="E40">
-        <v>133.3820000000001</v>
+        <v>170.4210000000003</v>
       </c>
       <c r="F40">
-        <v>1407.482</v>
+        <v>1444.521</v>
       </c>
       <c r="G40">
         <v>0</v>
@@ -4567,28 +4567,28 @@
         <v>231.925</v>
       </c>
       <c r="M40">
-        <v>106.6871356</v>
+        <v>109.4946918</v>
       </c>
       <c r="N40">
-        <v>125.2378643999999</v>
+        <v>122.4303081999999</v>
       </c>
       <c r="O40">
-        <v>27.55233016799999</v>
+        <v>26.93466780399999</v>
       </c>
       <c r="P40">
-        <v>97.68553423199995</v>
+        <v>95.49564039599994</v>
       </c>
       <c r="Q40">
-        <v>157.8855342319999</v>
+        <v>155.6956403959999</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1113535021367263</v>
+        <v>0.1122681956213283</v>
       </c>
       <c r="T40">
-        <v>0.8543818879425953</v>
+        <v>0.8663034103752654</v>
       </c>
       <c r="U40">
         <v>0.07580000000000001</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>2.173879715634618</v>
+        <v>2.118139210105525</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09154195932901028</v>
+        <v>0.09157762733325026</v>
       </c>
       <c r="C41">
-        <v>2263.343022394497</v>
+        <v>2223.415010504273</v>
       </c>
       <c r="D41">
-        <v>3707.864022394497</v>
+        <v>3704.975010504273</v>
       </c>
       <c r="E41">
-        <v>170.4210000000003</v>
+        <v>207.4600000000003</v>
       </c>
       <c r="F41">
-        <v>1444.521</v>
+        <v>1481.56</v>
       </c>
       <c r="G41">
         <v>0</v>
@@ -4649,28 +4649,28 @@
         <v>231.925</v>
       </c>
       <c r="M41">
-        <v>109.4946918</v>
+        <v>112.302248</v>
       </c>
       <c r="N41">
-        <v>122.4303081999999</v>
+        <v>119.6227519999999</v>
       </c>
       <c r="O41">
-        <v>26.93466780399999</v>
+        <v>26.31700543999998</v>
       </c>
       <c r="P41">
-        <v>95.49564039599994</v>
+        <v>93.30574655999995</v>
       </c>
       <c r="Q41">
-        <v>155.6956403959999</v>
+        <v>153.5057465599999</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1122681956213283</v>
+        <v>0.1132133788887504</v>
       </c>
       <c r="T41">
-        <v>0.8663034103752654</v>
+        <v>0.8786223168890243</v>
       </c>
       <c r="U41">
         <v>0.07580000000000001</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>2.118139210105525</v>
+        <v>2.065185729852887</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09157762733325026</v>
+        <v>0.09161329533749021</v>
       </c>
       <c r="C42">
-        <v>2223.415010504273</v>
+        <v>2183.49149710243</v>
       </c>
       <c r="D42">
-        <v>3704.975010504273</v>
+        <v>3702.09049710243</v>
       </c>
       <c r="E42">
-        <v>207.4600000000003</v>
+        <v>244.4990000000003</v>
       </c>
       <c r="F42">
-        <v>1481.56</v>
+        <v>1518.599</v>
       </c>
       <c r="G42">
         <v>0</v>
@@ -4731,28 +4731,28 @@
         <v>231.925</v>
       </c>
       <c r="M42">
-        <v>112.302248</v>
+        <v>115.1098042</v>
       </c>
       <c r="N42">
-        <v>119.6227519999999</v>
+        <v>116.8151957999999</v>
       </c>
       <c r="O42">
-        <v>26.31700543999998</v>
+        <v>25.69934307599998</v>
       </c>
       <c r="P42">
-        <v>93.30574655999995</v>
+        <v>91.11585272399995</v>
       </c>
       <c r="Q42">
-        <v>153.5057465599999</v>
+        <v>151.3158527239999</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1132133788887504</v>
+        <v>0.1141906022669326</v>
       </c>
       <c r="T42">
-        <v>0.8786223168890243</v>
+        <v>0.8913588134540971</v>
       </c>
       <c r="U42">
         <v>0.07580000000000001</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>2.065185729852887</v>
+        <v>2.014815346197938</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09161329533749021</v>
+        <v>0.09630088334173018</v>
       </c>
       <c r="C43">
-        <v>2183.49149710243</v>
+        <v>1802.817418733649</v>
       </c>
       <c r="D43">
-        <v>3702.09049710243</v>
+        <v>3358.455418733649</v>
       </c>
       <c r="E43">
-        <v>244.4990000000003</v>
+        <v>281.5380000000002</v>
       </c>
       <c r="F43">
-        <v>1518.599</v>
+        <v>1555.638</v>
       </c>
       <c r="G43">
         <v>0</v>
@@ -4813,45 +4813,45 @@
         <v>231.925</v>
       </c>
       <c r="M43">
-        <v>115.1098042</v>
+        <v>140.00742</v>
       </c>
       <c r="N43">
-        <v>116.8151957999999</v>
+        <v>91.91757999999996</v>
       </c>
       <c r="O43">
-        <v>25.69934307599998</v>
+        <v>20.22186759999999</v>
       </c>
       <c r="P43">
-        <v>91.11585272399995</v>
+        <v>71.69571239999996</v>
       </c>
       <c r="Q43">
-        <v>151.3158527239999</v>
+        <v>131.8957124</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1141906022669326</v>
+        <v>0.1152015230029831</v>
       </c>
       <c r="T43">
-        <v>0.8913588134540971</v>
+        <v>0.9045344995558966</v>
       </c>
       <c r="U43">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V43">
         <v>0.22</v>
       </c>
       <c r="W43">
-        <v>0.05912400000000001</v>
+        <v>0.0702</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y43">
-        <v>2.014815346197938</v>
+        <v>1.656519347331734</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09630088334173019</v>
+        <v>0.09644731134597015</v>
       </c>
       <c r="C44">
-        <v>1802.817418733649</v>
+        <v>1756.068684668304</v>
       </c>
       <c r="D44">
-        <v>3358.455418733648</v>
+        <v>3348.745684668304</v>
       </c>
       <c r="E44">
-        <v>281.538</v>
+        <v>318.577</v>
       </c>
       <c r="F44">
-        <v>1555.638</v>
+        <v>1592.677</v>
       </c>
       <c r="G44">
         <v>0</v>
@@ -4895,28 +4895,28 @@
         <v>231.925</v>
       </c>
       <c r="M44">
-        <v>140.00742</v>
+        <v>143.34093</v>
       </c>
       <c r="N44">
-        <v>91.91757999999996</v>
+        <v>88.58406999999997</v>
       </c>
       <c r="O44">
-        <v>20.22186759999999</v>
+        <v>19.48849539999999</v>
       </c>
       <c r="P44">
-        <v>71.69571239999996</v>
+        <v>69.09557459999998</v>
       </c>
       <c r="Q44">
-        <v>131.8957124</v>
+        <v>129.2955746</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1152015230029831</v>
+        <v>0.1162479146420529</v>
       </c>
       <c r="T44">
-        <v>0.9045344995558966</v>
+        <v>0.9181724904331978</v>
       </c>
       <c r="U44">
         <v>0.09</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>1.656519347331734</v>
+        <v>1.617995641579833</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09644731134597015</v>
+        <v>0.09659373935021012</v>
       </c>
       <c r="C45">
-        <v>1756.068684668304</v>
+        <v>1709.375932973979</v>
       </c>
       <c r="D45">
-        <v>3348.745684668304</v>
+        <v>3339.091932973979</v>
       </c>
       <c r="E45">
-        <v>318.577</v>
+        <v>355.6160000000002</v>
       </c>
       <c r="F45">
-        <v>1592.677</v>
+        <v>1629.716</v>
       </c>
       <c r="G45">
         <v>0</v>
@@ -4977,28 +4977,28 @@
         <v>231.925</v>
       </c>
       <c r="M45">
-        <v>143.34093</v>
+        <v>146.67444</v>
       </c>
       <c r="N45">
-        <v>88.58406999999997</v>
+        <v>85.25055999999995</v>
       </c>
       <c r="O45">
-        <v>19.48849539999999</v>
+        <v>18.75512319999999</v>
       </c>
       <c r="P45">
-        <v>69.09557459999998</v>
+        <v>66.49543679999996</v>
       </c>
       <c r="Q45">
-        <v>129.2955746</v>
+        <v>126.6954368</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1162479146420529</v>
+        <v>0.1173316774110895</v>
       </c>
       <c r="T45">
-        <v>0.9181724904331978</v>
+        <v>0.9322975524132598</v>
       </c>
       <c r="U45">
         <v>0.09</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>1.617995641579833</v>
+        <v>1.58122301336211</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09659373935021012</v>
+        <v>0.0967401673544501</v>
       </c>
       <c r="C46">
-        <v>1709.375932973979</v>
+        <v>1662.738680885071</v>
       </c>
       <c r="D46">
-        <v>3339.091932973979</v>
+        <v>3329.493680885071</v>
       </c>
       <c r="E46">
-        <v>355.6160000000002</v>
+        <v>392.6550000000002</v>
       </c>
       <c r="F46">
-        <v>1629.716</v>
+        <v>1666.755</v>
       </c>
       <c r="G46">
         <v>0</v>
@@ -5059,28 +5059,28 @@
         <v>231.925</v>
       </c>
       <c r="M46">
-        <v>146.67444</v>
+        <v>150.00795</v>
       </c>
       <c r="N46">
-        <v>85.25055999999995</v>
+        <v>81.91704999999996</v>
       </c>
       <c r="O46">
-        <v>18.75512319999999</v>
+        <v>18.02175099999999</v>
       </c>
       <c r="P46">
-        <v>66.49543679999996</v>
+        <v>63.89529899999997</v>
       </c>
       <c r="Q46">
-        <v>126.6954368</v>
+        <v>124.095299</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1173316774110895</v>
+        <v>0.1184548497353638</v>
       </c>
       <c r="T46">
-        <v>0.9322975524132598</v>
+        <v>0.9469362530107786</v>
       </c>
       <c r="U46">
         <v>0.09</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>1.58122301336211</v>
+        <v>1.546084724176285</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.0967401673544501</v>
+        <v>0.09688659535869004</v>
       </c>
       <c r="C47">
-        <v>1662.738680885071</v>
+        <v>1616.156451170926</v>
       </c>
       <c r="D47">
-        <v>3329.493680885071</v>
+        <v>3319.950451170926</v>
       </c>
       <c r="E47">
-        <v>392.6550000000002</v>
+        <v>429.6940000000002</v>
       </c>
       <c r="F47">
-        <v>1666.755</v>
+        <v>1703.794</v>
       </c>
       <c r="G47">
         <v>0</v>
@@ -5141,28 +5141,28 @@
         <v>231.925</v>
       </c>
       <c r="M47">
-        <v>150.00795</v>
+        <v>153.34146</v>
       </c>
       <c r="N47">
-        <v>81.91704999999996</v>
+        <v>78.58353999999994</v>
       </c>
       <c r="O47">
-        <v>18.02175099999999</v>
+        <v>17.28837879999999</v>
       </c>
       <c r="P47">
-        <v>63.89529899999997</v>
+        <v>61.29516119999995</v>
       </c>
       <c r="Q47">
-        <v>124.095299</v>
+        <v>121.4951611999999</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1184548497353638</v>
+        <v>0.1196196210346112</v>
       </c>
       <c r="T47">
-        <v>0.9469362530107786</v>
+        <v>0.9621171277045016</v>
       </c>
       <c r="U47">
         <v>0.09</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>1.546084724176285</v>
+        <v>1.512474186694192</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09688659535869004</v>
+        <v>0.1196834324809444</v>
       </c>
       <c r="C48">
-        <v>1616.156451170926</v>
+        <v>554.7420648646857</v>
       </c>
       <c r="D48">
-        <v>3319.950451170926</v>
+        <v>2295.575064864686</v>
       </c>
       <c r="E48">
-        <v>429.6940000000002</v>
+        <v>466.7330000000002</v>
       </c>
       <c r="F48">
-        <v>1703.794</v>
+        <v>1740.833</v>
       </c>
       <c r="G48">
         <v>0</v>
@@ -5223,45 +5223,45 @@
         <v>231.925</v>
       </c>
       <c r="M48">
-        <v>153.34146</v>
+        <v>255.5542844</v>
       </c>
       <c r="N48">
-        <v>78.58353999999994</v>
+        <v>-23.62928440000007</v>
       </c>
       <c r="O48">
-        <v>17.28837879999999</v>
+        <v>-5.198442568000016</v>
       </c>
       <c r="P48">
-        <v>61.29516119999995</v>
+        <v>-18.43084183200006</v>
       </c>
       <c r="Q48">
-        <v>121.4951611999999</v>
+        <v>41.76915816799993</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1196196210346112</v>
+        <v>0.1216283912704813</v>
       </c>
       <c r="T48">
-        <v>0.9621171277045016</v>
+        <v>0.9882981378812881</v>
       </c>
       <c r="U48">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V48">
-        <v>0.22</v>
+        <v>0.1996581670301278</v>
       </c>
       <c r="W48">
-        <v>0.0702</v>
+        <v>0.1174901810799772</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y48">
-        <v>1.512474186694192</v>
+        <v>0.9075371228642173</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1196834324809444</v>
+        <v>0.1206934324809444</v>
       </c>
       <c r="C49">
-        <v>554.7420648646857</v>
+        <v>486.7453328084969</v>
       </c>
       <c r="D49">
-        <v>2295.575064864686</v>
+        <v>2264.617332808497</v>
       </c>
       <c r="E49">
-        <v>466.7330000000002</v>
+        <v>503.7720000000002</v>
       </c>
       <c r="F49">
-        <v>1740.833</v>
+        <v>1777.872</v>
       </c>
       <c r="G49">
         <v>0</v>
@@ -5305,37 +5305,37 @@
         <v>231.925</v>
       </c>
       <c r="M49">
-        <v>255.5542844</v>
+        <v>260.9916096000001</v>
       </c>
       <c r="N49">
-        <v>-23.62928440000007</v>
+        <v>-29.06660960000011</v>
       </c>
       <c r="O49">
-        <v>-5.198442568000016</v>
+        <v>-6.394654112000024</v>
       </c>
       <c r="P49">
-        <v>-18.43084183200006</v>
+        <v>-22.67195548800008</v>
       </c>
       <c r="Q49">
-        <v>41.76915816799993</v>
+        <v>37.52804451199991</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1216283912704813</v>
+        <v>0.1230866295641444</v>
       </c>
       <c r="T49">
-        <v>0.9882981378812881</v>
+        <v>1.007303871302082</v>
       </c>
       <c r="U49">
         <v>0.1468</v>
       </c>
       <c r="V49">
-        <v>0.1996581670301278</v>
+        <v>0.1954986218836668</v>
       </c>
       <c r="W49">
-        <v>0.1174901810799772</v>
+        <v>0.1181008023074777</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.9075371228642173</v>
+        <v>0.8886300994712126</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1206934324809444</v>
+        <v>0.1217034324809444</v>
       </c>
       <c r="C50">
-        <v>486.7453328084969</v>
+        <v>419.5724715142692</v>
       </c>
       <c r="D50">
-        <v>2264.617332808497</v>
+        <v>2234.483471514269</v>
       </c>
       <c r="E50">
-        <v>503.7720000000002</v>
+        <v>540.8110000000001</v>
       </c>
       <c r="F50">
-        <v>1777.872</v>
+        <v>1814.911</v>
       </c>
       <c r="G50">
         <v>0</v>
@@ -5387,37 +5387,37 @@
         <v>231.925</v>
       </c>
       <c r="M50">
-        <v>260.9916096000001</v>
+        <v>266.4289348</v>
       </c>
       <c r="N50">
-        <v>-29.06660960000011</v>
+        <v>-34.50393480000008</v>
       </c>
       <c r="O50">
-        <v>-6.394654112000024</v>
+        <v>-7.590865656000018</v>
       </c>
       <c r="P50">
-        <v>-22.67195548800008</v>
+        <v>-26.91306914400006</v>
       </c>
       <c r="Q50">
-        <v>37.52804451199991</v>
+        <v>33.28693085599993</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1230866295641444</v>
+        <v>0.1246020536732453</v>
       </c>
       <c r="T50">
-        <v>1.007303871302082</v>
+        <v>1.027054927602123</v>
       </c>
       <c r="U50">
         <v>0.1468</v>
       </c>
       <c r="V50">
-        <v>0.1954986218836668</v>
+        <v>0.1915088540901226</v>
       </c>
       <c r="W50">
-        <v>0.1181008023074777</v>
+        <v>0.11868650021957</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.8886300994712126</v>
+        <v>0.8704947913187391</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1217034324809444</v>
+        <v>0.1227134324809444</v>
       </c>
       <c r="C51">
-        <v>419.5724715142692</v>
+        <v>353.1910246433852</v>
       </c>
       <c r="D51">
-        <v>2234.483471514269</v>
+        <v>2205.141024643385</v>
       </c>
       <c r="E51">
-        <v>540.8110000000001</v>
+        <v>577.8500000000001</v>
       </c>
       <c r="F51">
-        <v>1814.911</v>
+        <v>1851.95</v>
       </c>
       <c r="G51">
         <v>0</v>
@@ -5469,37 +5469,37 @@
         <v>231.925</v>
       </c>
       <c r="M51">
-        <v>266.4289348</v>
+        <v>271.86626</v>
       </c>
       <c r="N51">
-        <v>-34.50393480000008</v>
+        <v>-39.94126000000006</v>
       </c>
       <c r="O51">
-        <v>-7.590865656000018</v>
+        <v>-8.787077200000013</v>
       </c>
       <c r="P51">
-        <v>-26.91306914400006</v>
+        <v>-31.15418280000004</v>
       </c>
       <c r="Q51">
-        <v>33.28693085599993</v>
+        <v>29.04581719999995</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1246020536732453</v>
+        <v>0.1261780947467102</v>
       </c>
       <c r="T51">
-        <v>1.027054927602123</v>
+        <v>1.047596026154165</v>
       </c>
       <c r="U51">
         <v>0.1468</v>
       </c>
       <c r="V51">
-        <v>0.1915088540901226</v>
+        <v>0.1876786770083202</v>
       </c>
       <c r="W51">
-        <v>0.11868650021957</v>
+        <v>0.1192487702151786</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.8704947913187391</v>
+        <v>0.8530848954923643</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1227134324809444</v>
+        <v>0.1237234324809444</v>
       </c>
       <c r="C52">
-        <v>353.1910246433852</v>
+        <v>287.5702185809469</v>
       </c>
       <c r="D52">
-        <v>2205.141024643385</v>
+        <v>2176.559218580947</v>
       </c>
       <c r="E52">
-        <v>577.8500000000001</v>
+        <v>614.8890000000001</v>
       </c>
       <c r="F52">
-        <v>1851.95</v>
+        <v>1888.989</v>
       </c>
       <c r="G52">
         <v>0</v>
@@ -5551,37 +5551,37 @@
         <v>231.925</v>
       </c>
       <c r="M52">
-        <v>271.86626</v>
+        <v>277.3035852</v>
       </c>
       <c r="N52">
-        <v>-39.94126000000006</v>
+        <v>-45.37858520000009</v>
       </c>
       <c r="O52">
-        <v>-8.787077200000013</v>
+        <v>-9.983288744000019</v>
       </c>
       <c r="P52">
-        <v>-31.15418280000004</v>
+        <v>-35.39529645600007</v>
       </c>
       <c r="Q52">
-        <v>29.04581719999995</v>
+        <v>24.80470354399992</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1261780947467102</v>
+        <v>0.1278184640272553</v>
       </c>
       <c r="T52">
-        <v>1.047596026154165</v>
+        <v>1.068975536892006</v>
       </c>
       <c r="U52">
         <v>0.1468</v>
       </c>
       <c r="V52">
-        <v>0.1876786770083202</v>
+        <v>0.1839987029493335</v>
       </c>
       <c r="W52">
-        <v>0.1192487702151786</v>
+        <v>0.1197889904070378</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.8530848954923643</v>
+        <v>0.8363577406787884</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1237234324809444</v>
+        <v>0.1247334324809444</v>
       </c>
       <c r="C53">
-        <v>287.5702185809469</v>
+        <v>222.6808547785429</v>
       </c>
       <c r="D53">
-        <v>2176.559218580947</v>
+        <v>2148.708854778543</v>
       </c>
       <c r="E53">
-        <v>614.8890000000001</v>
+        <v>651.9280000000001</v>
       </c>
       <c r="F53">
-        <v>1888.989</v>
+        <v>1926.028</v>
       </c>
       <c r="G53">
         <v>0</v>
@@ -5633,37 +5633,37 @@
         <v>231.925</v>
       </c>
       <c r="M53">
-        <v>277.3035852</v>
+        <v>282.7409104</v>
       </c>
       <c r="N53">
-        <v>-45.37858520000009</v>
+        <v>-50.81591040000006</v>
       </c>
       <c r="O53">
-        <v>-9.983288744000019</v>
+        <v>-11.17950028800001</v>
       </c>
       <c r="P53">
-        <v>-35.39529645600007</v>
+        <v>-39.63641011200005</v>
       </c>
       <c r="Q53">
-        <v>24.80470354399992</v>
+        <v>20.56358988799994</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1278184640272553</v>
+        <v>0.1295271820278232</v>
       </c>
       <c r="T53">
-        <v>1.068975536892006</v>
+        <v>1.091245860577256</v>
       </c>
       <c r="U53">
         <v>0.1468</v>
       </c>
       <c r="V53">
-        <v>0.1839987029493335</v>
+        <v>0.180460266354154</v>
       </c>
       <c r="W53">
-        <v>0.1197889904070378</v>
+        <v>0.1203084328992102</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.8363577406787884</v>
+        <v>0.8202739379734272</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1247334324809444</v>
+        <v>0.1257434324809444</v>
       </c>
       <c r="C54">
-        <v>222.6808547785429</v>
+        <v>158.4952102578234</v>
       </c>
       <c r="D54">
-        <v>2148.708854778543</v>
+        <v>2121.562210257824</v>
       </c>
       <c r="E54">
-        <v>651.9280000000001</v>
+        <v>688.9670000000003</v>
       </c>
       <c r="F54">
-        <v>1926.028</v>
+        <v>1963.067</v>
       </c>
       <c r="G54">
         <v>0</v>
@@ -5715,37 +5715,37 @@
         <v>231.925</v>
       </c>
       <c r="M54">
-        <v>282.7409104</v>
+        <v>288.1782356000001</v>
       </c>
       <c r="N54">
-        <v>-50.81591040000006</v>
+        <v>-56.2532356000001</v>
       </c>
       <c r="O54">
-        <v>-11.17950028800001</v>
+        <v>-12.37571183200002</v>
       </c>
       <c r="P54">
-        <v>-39.63641011200005</v>
+        <v>-43.87752376800007</v>
       </c>
       <c r="Q54">
-        <v>20.56358988799994</v>
+        <v>16.32247623199991</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1295271820278232</v>
+        <v>0.1313086114326704</v>
       </c>
       <c r="T54">
-        <v>1.091245860577256</v>
+        <v>1.114463857610814</v>
       </c>
       <c r="U54">
         <v>0.1468</v>
       </c>
       <c r="V54">
-        <v>0.180460266354154</v>
+        <v>0.1770553556682265</v>
       </c>
       <c r="W54">
-        <v>0.1203084328992102</v>
+        <v>0.1208082737879044</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.8202739379734272</v>
+        <v>0.8047970712192115</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1257434324809444</v>
+        <v>0.1570326577233548</v>
       </c>
       <c r="C55">
-        <v>158.4952102578234</v>
+        <v>-475.3292951972467</v>
       </c>
       <c r="D55">
-        <v>2121.562210257824</v>
+        <v>1524.776704802754</v>
       </c>
       <c r="E55">
-        <v>688.9670000000003</v>
+        <v>726.0060000000003</v>
       </c>
       <c r="F55">
-        <v>1963.067</v>
+        <v>2000.106</v>
       </c>
       <c r="G55">
         <v>0</v>
@@ -5797,45 +5797,45 @@
         <v>231.925</v>
       </c>
       <c r="M55">
-        <v>288.1782356000001</v>
+        <v>401.6212848000001</v>
       </c>
       <c r="N55">
-        <v>-56.2532356000001</v>
+        <v>-169.6962848000001</v>
       </c>
       <c r="O55">
-        <v>-12.37571183200002</v>
+        <v>-37.33318265600003</v>
       </c>
       <c r="P55">
-        <v>-43.87752376800007</v>
+        <v>-132.3631021440001</v>
       </c>
       <c r="Q55">
-        <v>16.32247623199991</v>
+        <v>-72.16310214400011</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1313086114326704</v>
+        <v>0.1356005926429685</v>
       </c>
       <c r="T55">
-        <v>1.114463857610814</v>
+        <v>1.170402760795884</v>
       </c>
       <c r="U55">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V55">
-        <v>0.1770553556682265</v>
+        <v>0.1270438144865971</v>
       </c>
       <c r="W55">
-        <v>0.1208082737879044</v>
+        <v>0.1752896020510913</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y55">
-        <v>0.8047970712192115</v>
+        <v>0.5774718840299868</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1570326577233548</v>
+        <v>0.1585826577233548</v>
       </c>
       <c r="C56">
-        <v>-475.3292951972467</v>
+        <v>-533.3236791202025</v>
       </c>
       <c r="D56">
-        <v>1524.776704802754</v>
+        <v>1503.821320879798</v>
       </c>
       <c r="E56">
-        <v>726.0060000000003</v>
+        <v>763.0450000000003</v>
       </c>
       <c r="F56">
-        <v>2000.106</v>
+        <v>2037.145</v>
       </c>
       <c r="G56">
         <v>0</v>
@@ -5879,37 +5879,37 @@
         <v>231.925</v>
       </c>
       <c r="M56">
-        <v>401.6212848000001</v>
+        <v>409.0587160000001</v>
       </c>
       <c r="N56">
-        <v>-169.6962848000001</v>
+        <v>-177.1337160000001</v>
       </c>
       <c r="O56">
-        <v>-37.33318265600003</v>
+        <v>-38.96941752000002</v>
       </c>
       <c r="P56">
-        <v>-132.3631021440001</v>
+        <v>-138.1642984800001</v>
       </c>
       <c r="Q56">
-        <v>-72.16310214400011</v>
+        <v>-77.96429848000008</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1356005926429685</v>
+        <v>0.1375961613683678</v>
       </c>
       <c r="T56">
-        <v>1.170402760795884</v>
+        <v>1.196411711035793</v>
       </c>
       <c r="U56">
         <v>0.2008</v>
       </c>
       <c r="V56">
-        <v>0.1270438144865971</v>
+        <v>0.1247339269504772</v>
       </c>
       <c r="W56">
-        <v>0.1752896020510913</v>
+        <v>0.1757534274683442</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.5774718840299868</v>
+        <v>0.5669723952294417</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1585826577233548</v>
+        <v>0.1601326577233548</v>
       </c>
       <c r="C57">
-        <v>-533.3236791202025</v>
+        <v>-590.7498816376467</v>
       </c>
       <c r="D57">
-        <v>1503.821320879798</v>
+        <v>1483.434118362354</v>
       </c>
       <c r="E57">
-        <v>763.0450000000003</v>
+        <v>800.0840000000003</v>
       </c>
       <c r="F57">
-        <v>2037.145</v>
+        <v>2074.184</v>
       </c>
       <c r="G57">
         <v>0</v>
@@ -5961,37 +5961,37 @@
         <v>231.925</v>
       </c>
       <c r="M57">
-        <v>409.0587160000001</v>
+        <v>416.4961472000001</v>
       </c>
       <c r="N57">
-        <v>-177.1337160000001</v>
+        <v>-184.5711472000001</v>
       </c>
       <c r="O57">
-        <v>-38.96941752000002</v>
+        <v>-40.60565238400002</v>
       </c>
       <c r="P57">
-        <v>-138.1642984800001</v>
+        <v>-143.9654948160001</v>
       </c>
       <c r="Q57">
-        <v>-77.96429848000008</v>
+        <v>-83.76549481600009</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1375961613683678</v>
+        <v>0.1396824377631034</v>
       </c>
       <c r="T57">
-        <v>1.196411711035793</v>
+        <v>1.223602886286606</v>
       </c>
       <c r="U57">
         <v>0.2008</v>
       </c>
       <c r="V57">
-        <v>0.1247339269504772</v>
+        <v>0.1225065353977901</v>
       </c>
       <c r="W57">
-        <v>0.1757534274683442</v>
+        <v>0.1762006876921237</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.5669723952294417</v>
+        <v>0.5568478881717731</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1601326577233548</v>
+        <v>0.1616826577233548</v>
       </c>
       <c r="C58">
-        <v>-590.7498816376467</v>
+        <v>-647.6307020500749</v>
       </c>
       <c r="D58">
-        <v>1483.434118362354</v>
+        <v>1463.592297949926</v>
       </c>
       <c r="E58">
-        <v>800.0840000000003</v>
+        <v>837.1230000000005</v>
       </c>
       <c r="F58">
-        <v>2074.184</v>
+        <v>2111.223</v>
       </c>
       <c r="G58">
         <v>0</v>
@@ -6043,37 +6043,37 @@
         <v>231.925</v>
       </c>
       <c r="M58">
-        <v>416.4961472000001</v>
+        <v>423.9335784000001</v>
       </c>
       <c r="N58">
-        <v>-184.5711472000001</v>
+        <v>-192.0085784000001</v>
       </c>
       <c r="O58">
-        <v>-40.60565238400002</v>
+        <v>-42.24188724800003</v>
       </c>
       <c r="P58">
-        <v>-143.9654948160001</v>
+        <v>-149.7666911520001</v>
       </c>
       <c r="Q58">
-        <v>-83.76549481600009</v>
+        <v>-89.56669115200012</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1396824377631034</v>
+        <v>0.1418657502692222</v>
       </c>
       <c r="T58">
-        <v>1.223602886286606</v>
+        <v>1.252058767363039</v>
       </c>
       <c r="U58">
         <v>0.2008</v>
       </c>
       <c r="V58">
-        <v>0.1225065353977901</v>
+        <v>0.1203572979346709</v>
       </c>
       <c r="W58">
-        <v>0.1762006876921237</v>
+        <v>0.1766322545747181</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.5568478881717731</v>
+        <v>0.547078626975777</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1616826577233548</v>
+        <v>0.1632326577233548</v>
       </c>
       <c r="C59">
-        <v>-647.6307020500749</v>
+        <v>-703.9877359411803</v>
       </c>
       <c r="D59">
-        <v>1463.592297949926</v>
+        <v>1444.27426405882</v>
       </c>
       <c r="E59">
-        <v>837.1230000000005</v>
+        <v>874.1620000000003</v>
       </c>
       <c r="F59">
-        <v>2111.223</v>
+        <v>2148.262</v>
       </c>
       <c r="G59">
         <v>0</v>
@@ -6125,37 +6125,37 @@
         <v>231.925</v>
       </c>
       <c r="M59">
-        <v>423.9335784000001</v>
+        <v>431.3710096</v>
       </c>
       <c r="N59">
-        <v>-192.0085784000001</v>
+        <v>-199.4460096000001</v>
       </c>
       <c r="O59">
-        <v>-42.24188724800003</v>
+        <v>-43.87812211200002</v>
       </c>
       <c r="P59">
-        <v>-149.7666911520001</v>
+        <v>-155.5678874880001</v>
       </c>
       <c r="Q59">
-        <v>-89.56669115200012</v>
+        <v>-95.36788748800006</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1418657502692222</v>
+        <v>0.144153030037537</v>
       </c>
       <c r="T59">
-        <v>1.252058767363039</v>
+        <v>1.281869690395492</v>
       </c>
       <c r="U59">
         <v>0.2008</v>
       </c>
       <c r="V59">
-        <v>0.1203572979346709</v>
+        <v>0.1182821721082111</v>
       </c>
       <c r="W59">
-        <v>0.1766322545747181</v>
+        <v>0.1770489398406712</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.547078626975777</v>
+        <v>0.5376462368555051</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1632326577233548</v>
+        <v>0.1647826577233548</v>
       </c>
       <c r="C60">
-        <v>-703.9877359411798</v>
+        <v>-759.8414535826043</v>
       </c>
       <c r="D60">
-        <v>1444.27426405882</v>
+        <v>1425.459546417396</v>
       </c>
       <c r="E60">
-        <v>874.1619999999998</v>
+        <v>911.201</v>
       </c>
       <c r="F60">
-        <v>2148.262</v>
+        <v>2185.301</v>
       </c>
       <c r="G60">
         <v>0</v>
@@ -6207,37 +6207,37 @@
         <v>231.925</v>
       </c>
       <c r="M60">
-        <v>431.3710096</v>
+        <v>438.8084408</v>
       </c>
       <c r="N60">
-        <v>-199.4460096</v>
+        <v>-206.8834408000001</v>
       </c>
       <c r="O60">
-        <v>-43.87812211200001</v>
+        <v>-45.51435697600002</v>
       </c>
       <c r="P60">
-        <v>-155.567887488</v>
+        <v>-161.3690838240001</v>
       </c>
       <c r="Q60">
-        <v>-95.36788748800004</v>
+        <v>-101.1690838240001</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1441530300375369</v>
+        <v>0.1465518844286964</v>
       </c>
       <c r="T60">
-        <v>1.281869690395492</v>
+        <v>1.313134804795382</v>
       </c>
       <c r="U60">
         <v>0.2008</v>
       </c>
       <c r="V60">
-        <v>0.1182821721082111</v>
+        <v>0.1162773895301058</v>
       </c>
       <c r="W60">
-        <v>0.1770489398406712</v>
+        <v>0.1774515001823548</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.5376462368555051</v>
+        <v>0.5285335887732083</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1647826577233548</v>
+        <v>0.1663326577233548</v>
       </c>
       <c r="C61">
-        <v>-759.8414535826043</v>
+        <v>-815.211272289167</v>
       </c>
       <c r="D61">
-        <v>1425.459546417396</v>
+        <v>1407.128727710833</v>
       </c>
       <c r="E61">
-        <v>911.201</v>
+        <v>948.2400000000002</v>
       </c>
       <c r="F61">
-        <v>2185.301</v>
+        <v>2222.34</v>
       </c>
       <c r="G61">
         <v>0</v>
@@ -6289,37 +6289,37 @@
         <v>231.925</v>
       </c>
       <c r="M61">
-        <v>438.8084408</v>
+        <v>446.245872</v>
       </c>
       <c r="N61">
-        <v>-206.8834408000001</v>
+        <v>-214.3208720000001</v>
       </c>
       <c r="O61">
-        <v>-45.51435697600002</v>
+        <v>-47.15059184000001</v>
       </c>
       <c r="P61">
-        <v>-161.3690838240001</v>
+        <v>-167.1702801600001</v>
       </c>
       <c r="Q61">
-        <v>-101.1690838240001</v>
+        <v>-106.9702801600001</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1465518844286964</v>
+        <v>0.1490706815394138</v>
       </c>
       <c r="T61">
-        <v>1.313134804795382</v>
+        <v>1.345963174915267</v>
       </c>
       <c r="U61">
         <v>0.2008</v>
       </c>
       <c r="V61">
-        <v>0.1162773895301058</v>
+        <v>0.1143394330379374</v>
       </c>
       <c r="W61">
-        <v>0.1774515001823548</v>
+        <v>0.1778406418459822</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.5285335887732083</v>
+        <v>0.5197246956269882</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1663326577233548</v>
+        <v>0.1678826577233548</v>
       </c>
       <c r="C62">
-        <v>-815.211272289167</v>
+        <v>-870.1156232622275</v>
       </c>
       <c r="D62">
-        <v>1407.128727710833</v>
+        <v>1389.263376737772</v>
       </c>
       <c r="E62">
-        <v>948.2400000000002</v>
+        <v>985.279</v>
       </c>
       <c r="F62">
-        <v>2222.34</v>
+        <v>2259.379</v>
       </c>
       <c r="G62">
         <v>0</v>
@@ -6371,37 +6371,37 @@
         <v>231.925</v>
       </c>
       <c r="M62">
-        <v>446.245872</v>
+        <v>453.6833032</v>
       </c>
       <c r="N62">
-        <v>-214.3208720000001</v>
+        <v>-221.7583032000001</v>
       </c>
       <c r="O62">
-        <v>-47.15059184000001</v>
+        <v>-48.78682670400001</v>
       </c>
       <c r="P62">
-        <v>-167.1702801600001</v>
+        <v>-172.971476496</v>
       </c>
       <c r="Q62">
-        <v>-106.9702801600001</v>
+        <v>-112.771476496</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1490706815394138</v>
+        <v>0.1517186477327321</v>
       </c>
       <c r="T62">
-        <v>1.345963174915267</v>
+        <v>1.380475051195145</v>
       </c>
       <c r="U62">
         <v>0.2008</v>
       </c>
       <c r="V62">
-        <v>0.1143394330379374</v>
+        <v>0.1124650161028893</v>
       </c>
       <c r="W62">
-        <v>0.1778406418459822</v>
+        <v>0.1782170247665398</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.5197246956269882</v>
+        <v>0.5112046186494966</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1678826577233548</v>
+        <v>0.1694326577233548</v>
       </c>
       <c r="C63">
-        <v>-870.1156232622275</v>
+        <v>-924.5720134049036</v>
       </c>
       <c r="D63">
-        <v>1389.263376737772</v>
+        <v>1371.845986595097</v>
       </c>
       <c r="E63">
-        <v>985.279</v>
+        <v>1022.318</v>
       </c>
       <c r="F63">
-        <v>2259.379</v>
+        <v>2296.418</v>
       </c>
       <c r="G63">
         <v>0</v>
@@ -6453,37 +6453,37 @@
         <v>231.925</v>
       </c>
       <c r="M63">
-        <v>453.6833032</v>
+        <v>461.1207344000001</v>
       </c>
       <c r="N63">
-        <v>-221.7583032000001</v>
+        <v>-229.1957344000001</v>
       </c>
       <c r="O63">
-        <v>-48.78682670400001</v>
+        <v>-50.42306156800002</v>
       </c>
       <c r="P63">
-        <v>-172.971476496</v>
+        <v>-178.7726728320001</v>
       </c>
       <c r="Q63">
-        <v>-112.771476496</v>
+        <v>-118.5726728320001</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1517186477327321</v>
+        <v>0.154505980567804</v>
       </c>
       <c r="T63">
-        <v>1.380475051195145</v>
+        <v>1.41680334201607</v>
       </c>
       <c r="U63">
         <v>0.2008</v>
       </c>
       <c r="V63">
-        <v>0.1124650161028893</v>
+        <v>0.110651064230262</v>
       </c>
       <c r="W63">
-        <v>0.1782170247665398</v>
+        <v>0.1785812663025634</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.5112046186494966</v>
+        <v>0.5029593828648273</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1694326577233548</v>
+        <v>0.1934842786274092</v>
       </c>
       <c r="C64">
-        <v>-924.5720134049036</v>
+        <v>-1185.027614785858</v>
       </c>
       <c r="D64">
-        <v>1371.845986595097</v>
+        <v>1148.429385214142</v>
       </c>
       <c r="E64">
-        <v>1022.318</v>
+        <v>1059.357</v>
       </c>
       <c r="F64">
-        <v>2296.418</v>
+        <v>2333.457</v>
       </c>
       <c r="G64">
         <v>0</v>
@@ -6535,45 +6535,45 @@
         <v>231.925</v>
       </c>
       <c r="M64">
-        <v>461.1207344000001</v>
+        <v>550.2291606</v>
       </c>
       <c r="N64">
-        <v>-229.1957344000001</v>
+        <v>-318.3041606</v>
       </c>
       <c r="O64">
-        <v>-50.42306156800002</v>
+        <v>-70.02691533200002</v>
       </c>
       <c r="P64">
-        <v>-178.7726728320001</v>
+        <v>-248.277245268</v>
       </c>
       <c r="Q64">
-        <v>-118.5726728320001</v>
+        <v>-188.077245268</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.154505980567804</v>
+        <v>0.1586645770805942</v>
       </c>
       <c r="T64">
-        <v>1.41680334201607</v>
+        <v>1.471003795446896</v>
       </c>
       <c r="U64">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.110651064230262</v>
+        <v>0.09273136295495712</v>
       </c>
       <c r="W64">
-        <v>0.1785812663025634</v>
+        <v>0.2139339446152211</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y64">
-        <v>0.5029593828648273</v>
+        <v>0.421506195249805</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1934842786274092</v>
+        <v>0.1953842786274092</v>
       </c>
       <c r="C65">
-        <v>-1185.027614785858</v>
+        <v>-1236.653815071404</v>
       </c>
       <c r="D65">
-        <v>1148.429385214142</v>
+        <v>1133.842184928596</v>
       </c>
       <c r="E65">
-        <v>1059.357</v>
+        <v>1096.396</v>
       </c>
       <c r="F65">
-        <v>2333.457</v>
+        <v>2370.496</v>
       </c>
       <c r="G65">
         <v>0</v>
@@ -6617,37 +6617,37 @@
         <v>231.925</v>
       </c>
       <c r="M65">
-        <v>550.2291606</v>
+        <v>558.9629568</v>
       </c>
       <c r="N65">
-        <v>-318.3041606</v>
+        <v>-327.0379568000001</v>
       </c>
       <c r="O65">
-        <v>-70.02691533200002</v>
+        <v>-71.94835049600002</v>
       </c>
       <c r="P65">
-        <v>-248.277245268</v>
+        <v>-255.0896063040001</v>
       </c>
       <c r="Q65">
-        <v>-188.077245268</v>
+        <v>-194.8896063040001</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1586645770805942</v>
+        <v>0.1617997042217218</v>
       </c>
       <c r="T65">
-        <v>1.471003795446896</v>
+        <v>1.511865011987088</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.09273136295495712</v>
+        <v>0.0912824354087859</v>
       </c>
       <c r="W65">
-        <v>0.2139339446152211</v>
+        <v>0.2142756017306083</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.421506195249805</v>
+        <v>0.4149201609490268</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1953842786274092</v>
+        <v>0.1972842786274092</v>
       </c>
       <c r="C66">
-        <v>-1236.653815071404</v>
+        <v>-1287.914093813227</v>
       </c>
       <c r="D66">
-        <v>1133.842184928596</v>
+        <v>1119.620906186773</v>
       </c>
       <c r="E66">
-        <v>1096.396</v>
+        <v>1133.435</v>
       </c>
       <c r="F66">
-        <v>2370.496</v>
+        <v>2407.535</v>
       </c>
       <c r="G66">
         <v>0</v>
@@ -6699,37 +6699,37 @@
         <v>231.925</v>
       </c>
       <c r="M66">
-        <v>558.9629568</v>
+        <v>567.6967530000001</v>
       </c>
       <c r="N66">
-        <v>-327.0379568000001</v>
+        <v>-335.7717530000001</v>
       </c>
       <c r="O66">
-        <v>-71.94835049600002</v>
+        <v>-73.86978566000002</v>
       </c>
       <c r="P66">
-        <v>-255.0896063040001</v>
+        <v>-261.9019673400001</v>
       </c>
       <c r="Q66">
-        <v>-194.8896063040001</v>
+        <v>-201.7019673400001</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1617997042217218</v>
+        <v>0.1651139814851996</v>
       </c>
       <c r="T66">
-        <v>1.511865011987088</v>
+        <v>1.555061155186719</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.0912824354087859</v>
+        <v>0.08987809024865075</v>
       </c>
       <c r="W66">
-        <v>0.2142756017306083</v>
+        <v>0.2146067463193682</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.4149201609490268</v>
+        <v>0.4085367738575033</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1972842786274092</v>
+        <v>0.1991842786274092</v>
       </c>
       <c r="C67">
-        <v>-1287.914093813227</v>
+        <v>-1338.82204922894</v>
       </c>
       <c r="D67">
-        <v>1119.620906186773</v>
+        <v>1105.75195077106</v>
       </c>
       <c r="E67">
-        <v>1133.435</v>
+        <v>1170.474</v>
       </c>
       <c r="F67">
-        <v>2407.535</v>
+        <v>2444.574</v>
       </c>
       <c r="G67">
         <v>0</v>
@@ -6781,37 +6781,37 @@
         <v>231.925</v>
       </c>
       <c r="M67">
-        <v>567.6967530000001</v>
+        <v>576.4305492000001</v>
       </c>
       <c r="N67">
-        <v>-335.7717530000001</v>
+        <v>-344.5055492000001</v>
       </c>
       <c r="O67">
-        <v>-73.86978566000002</v>
+        <v>-75.79122082400004</v>
       </c>
       <c r="P67">
-        <v>-261.9019673400001</v>
+        <v>-268.7143283760001</v>
       </c>
       <c r="Q67">
-        <v>-201.7019673400001</v>
+        <v>-208.5143283760001</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1651139814851996</v>
+        <v>0.1686232162347643</v>
       </c>
       <c r="T67">
-        <v>1.555061155186719</v>
+        <v>1.600798247986329</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.08987809024865075</v>
+        <v>0.08851630100245905</v>
       </c>
       <c r="W67">
-        <v>0.2146067463193682</v>
+        <v>0.2149278562236202</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.4085367738575033</v>
+        <v>0.4023468227384502</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1991842786274092</v>
+        <v>0.2010842786274092</v>
       </c>
       <c r="C68">
-        <v>-1338.82204922894</v>
+        <v>-1389.390614005462</v>
       </c>
       <c r="D68">
-        <v>1105.75195077106</v>
+        <v>1092.222385994539</v>
       </c>
       <c r="E68">
-        <v>1170.474</v>
+        <v>1207.513</v>
       </c>
       <c r="F68">
-        <v>2444.574</v>
+        <v>2481.613</v>
       </c>
       <c r="G68">
         <v>0</v>
@@ -6863,37 +6863,37 @@
         <v>231.925</v>
       </c>
       <c r="M68">
-        <v>576.4305492000001</v>
+        <v>585.1643454000001</v>
       </c>
       <c r="N68">
-        <v>-344.5055492000001</v>
+        <v>-353.2393454000002</v>
       </c>
       <c r="O68">
-        <v>-75.79122082400004</v>
+        <v>-77.71265598800004</v>
       </c>
       <c r="P68">
-        <v>-268.7143283760001</v>
+        <v>-275.5266894120001</v>
       </c>
       <c r="Q68">
-        <v>-208.5143283760001</v>
+        <v>-215.3266894120001</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1686232162347643</v>
+        <v>0.172345131878242</v>
       </c>
       <c r="T68">
-        <v>1.600798247986329</v>
+        <v>1.649307285804096</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.08851630100245905</v>
+        <v>0.08719516218152683</v>
       </c>
       <c r="W68">
-        <v>0.2149278562236202</v>
+        <v>0.215239380757596</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.4023468227384502</v>
+        <v>0.3963416462796674</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2010842786274092</v>
+        <v>0.2029842786274092</v>
       </c>
       <c r="C69">
-        <v>-1389.390614005462</v>
+        <v>-1439.632095522769</v>
       </c>
       <c r="D69">
-        <v>1092.222385994539</v>
+        <v>1079.019904477231</v>
       </c>
       <c r="E69">
-        <v>1207.513</v>
+        <v>1244.552</v>
       </c>
       <c r="F69">
-        <v>2481.613</v>
+        <v>2518.652</v>
       </c>
       <c r="G69">
         <v>0</v>
@@ -6945,37 +6945,37 @@
         <v>231.925</v>
       </c>
       <c r="M69">
-        <v>585.1643454000001</v>
+        <v>593.8981416</v>
       </c>
       <c r="N69">
-        <v>-353.2393454000002</v>
+        <v>-361.9731416000001</v>
       </c>
       <c r="O69">
-        <v>-77.71265598800004</v>
+        <v>-79.63409115200001</v>
       </c>
       <c r="P69">
-        <v>-275.5266894120001</v>
+        <v>-282.3390504480001</v>
       </c>
       <c r="Q69">
-        <v>-215.3266894120001</v>
+        <v>-222.1390504480001</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.172345131878242</v>
+        <v>0.1762996672494371</v>
       </c>
       <c r="T69">
-        <v>1.649307285804096</v>
+        <v>1.700848138485474</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.08719516218152683</v>
+        <v>0.08591288038473968</v>
       </c>
       <c r="W69">
-        <v>0.215239380757596</v>
+        <v>0.2155417428052784</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.3963416462796674</v>
+        <v>0.3905130926579077</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2029842786274092</v>
+        <v>0.2048842786274092</v>
       </c>
       <c r="C70">
-        <v>-1439.632095522769</v>
+        <v>-1489.558213195209</v>
       </c>
       <c r="D70">
-        <v>1079.019904477231</v>
+        <v>1066.132786804791</v>
       </c>
       <c r="E70">
-        <v>1244.552</v>
+        <v>1281.591</v>
       </c>
       <c r="F70">
-        <v>2518.652</v>
+        <v>2555.691</v>
       </c>
       <c r="G70">
         <v>0</v>
@@ -7027,37 +7027,37 @@
         <v>231.925</v>
       </c>
       <c r="M70">
-        <v>593.8981416</v>
+        <v>602.6319378000001</v>
       </c>
       <c r="N70">
-        <v>-361.9731416000001</v>
+        <v>-370.7069378000001</v>
       </c>
       <c r="O70">
-        <v>-79.63409115200001</v>
+        <v>-81.55552631600003</v>
       </c>
       <c r="P70">
-        <v>-282.3390504480001</v>
+        <v>-289.1514114840001</v>
       </c>
       <c r="Q70">
-        <v>-222.1390504480001</v>
+        <v>-228.9514114840001</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1762996672494371</v>
+        <v>0.1805093339349028</v>
       </c>
       <c r="T70">
-        <v>1.700848138485474</v>
+        <v>1.755714207468877</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.08591288038473968</v>
+        <v>0.08466776617626519</v>
       </c>
       <c r="W70">
-        <v>0.2155417428052784</v>
+        <v>0.2158353407356367</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.3905130926579077</v>
+        <v>0.3848534826193872</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2048842786274092</v>
+        <v>0.2067842786274092</v>
       </c>
       <c r="C71">
-        <v>-1489.558213195209</v>
+        <v>-1539.180133168516</v>
       </c>
       <c r="D71">
-        <v>1066.132786804791</v>
+        <v>1053.549866831485</v>
       </c>
       <c r="E71">
-        <v>1281.591</v>
+        <v>1318.630000000001</v>
       </c>
       <c r="F71">
-        <v>2555.691</v>
+        <v>2592.73</v>
       </c>
       <c r="G71">
         <v>0</v>
@@ -7109,37 +7109,37 @@
         <v>231.925</v>
       </c>
       <c r="M71">
-        <v>602.6319378000001</v>
+        <v>611.3657340000001</v>
       </c>
       <c r="N71">
-        <v>-370.7069378000001</v>
+        <v>-379.4407340000001</v>
       </c>
       <c r="O71">
-        <v>-81.55552631600003</v>
+        <v>-83.47696148000003</v>
       </c>
       <c r="P71">
-        <v>-289.1514114840001</v>
+        <v>-295.9637725200001</v>
       </c>
       <c r="Q71">
-        <v>-228.9514114840001</v>
+        <v>-235.7637725200001</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1805093339349028</v>
+        <v>0.1849996450660662</v>
       </c>
       <c r="T71">
-        <v>1.755714207468877</v>
+        <v>1.814238014384506</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.08466776617626519</v>
+        <v>0.0834582266594614</v>
       </c>
       <c r="W71">
-        <v>0.2158353407356367</v>
+        <v>0.216120550153699</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.3848534826193872</v>
+        <v>0.3793555757248245</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2067842786274092</v>
+        <v>0.2086842786274092</v>
       </c>
       <c r="C72">
-        <v>-1539.180133168516</v>
+        <v>-1588.508500588429</v>
       </c>
       <c r="D72">
-        <v>1053.549866831485</v>
+        <v>1041.260499411571</v>
       </c>
       <c r="E72">
-        <v>1318.630000000001</v>
+        <v>1355.669</v>
       </c>
       <c r="F72">
-        <v>2592.73</v>
+        <v>2629.769</v>
       </c>
       <c r="G72">
         <v>0</v>
@@ -7191,37 +7191,37 @@
         <v>231.925</v>
       </c>
       <c r="M72">
-        <v>611.3657340000001</v>
+        <v>620.0995302000001</v>
       </c>
       <c r="N72">
-        <v>-379.4407340000001</v>
+        <v>-388.1745302000002</v>
       </c>
       <c r="O72">
-        <v>-83.47696148000003</v>
+        <v>-85.39839664400003</v>
       </c>
       <c r="P72">
-        <v>-295.9637725200001</v>
+        <v>-302.7761335560001</v>
       </c>
       <c r="Q72">
-        <v>-235.7637725200001</v>
+        <v>-242.5761335560001</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1849996450660662</v>
+        <v>0.1897996328269651</v>
       </c>
       <c r="T72">
-        <v>1.814238014384506</v>
+        <v>1.876797945915006</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.0834582266594614</v>
+        <v>0.08228275867834221</v>
       </c>
       <c r="W72">
-        <v>0.216120550153699</v>
+        <v>0.2163977255036469</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.3793555757248245</v>
+        <v>0.3740125394470101</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2086842786274092</v>
+        <v>0.2105842786274092</v>
       </c>
       <c r="C73">
-        <v>-1588.508500588429</v>
+        <v>-1637.553469636941</v>
       </c>
       <c r="D73">
-        <v>1041.260499411571</v>
+        <v>1029.254530363059</v>
       </c>
       <c r="E73">
-        <v>1355.669</v>
+        <v>1392.708</v>
       </c>
       <c r="F73">
-        <v>2629.769</v>
+        <v>2666.808</v>
       </c>
       <c r="G73">
         <v>0</v>
@@ -7273,37 +7273,37 @@
         <v>231.925</v>
       </c>
       <c r="M73">
-        <v>620.0995302</v>
+        <v>628.8333264</v>
       </c>
       <c r="N73">
-        <v>-388.1745302</v>
+        <v>-396.9083264000001</v>
       </c>
       <c r="O73">
-        <v>-85.39839664400002</v>
+        <v>-87.31983180800002</v>
       </c>
       <c r="P73">
-        <v>-302.776133556</v>
+        <v>-309.5884945920001</v>
       </c>
       <c r="Q73">
-        <v>-242.5761335560001</v>
+        <v>-249.3884945920001</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.189799632826965</v>
+        <v>0.1949424768564995</v>
       </c>
       <c r="T73">
-        <v>1.876797945915005</v>
+        <v>1.943826443983399</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.08228275867834223</v>
+        <v>0.08113994258558747</v>
       </c>
       <c r="W73">
-        <v>0.2163977255036469</v>
+        <v>0.2166672015383185</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.3740125394470102</v>
+        <v>0.3688179208435794</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2105842786274092</v>
+        <v>0.2124842786274092</v>
       </c>
       <c r="C74">
-        <v>-1637.553469636941</v>
+        <v>-1686.324731514266</v>
       </c>
       <c r="D74">
-        <v>1029.254530363059</v>
+        <v>1017.522268485734</v>
       </c>
       <c r="E74">
-        <v>1392.708</v>
+        <v>1429.747</v>
       </c>
       <c r="F74">
-        <v>2666.808</v>
+        <v>2703.847</v>
       </c>
       <c r="G74">
         <v>0</v>
@@ -7355,37 +7355,37 @@
         <v>231.925</v>
       </c>
       <c r="M74">
-        <v>628.8333264</v>
+        <v>637.5671226000001</v>
       </c>
       <c r="N74">
-        <v>-396.9083264000001</v>
+        <v>-405.6421226000001</v>
       </c>
       <c r="O74">
-        <v>-87.31983180800002</v>
+        <v>-89.24126697200002</v>
       </c>
       <c r="P74">
-        <v>-309.5884945920001</v>
+        <v>-316.4008556280001</v>
       </c>
       <c r="Q74">
-        <v>-249.3884945920001</v>
+        <v>-256.2008556280001</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1949424768564995</v>
+        <v>0.2004662722956291</v>
       </c>
       <c r="T74">
-        <v>1.943826443983399</v>
+        <v>2.015820015982784</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.08113994258558747</v>
+        <v>0.0800284365227712</v>
       </c>
       <c r="W74">
-        <v>0.2166672015383185</v>
+        <v>0.2169292946679305</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3688179208435794</v>
+        <v>0.363765620558051</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2124842786274092</v>
+        <v>0.2143842786274092</v>
       </c>
       <c r="C75">
-        <v>-1686.324731514266</v>
+        <v>-1734.831540528626</v>
       </c>
       <c r="D75">
-        <v>1017.522268485734</v>
+        <v>1006.054459471374</v>
       </c>
       <c r="E75">
-        <v>1429.747</v>
+        <v>1466.786</v>
       </c>
       <c r="F75">
-        <v>2703.847</v>
+        <v>2740.886</v>
       </c>
       <c r="G75">
         <v>0</v>
@@ -7437,37 +7437,37 @@
         <v>231.925</v>
       </c>
       <c r="M75">
-        <v>637.5671226000001</v>
+        <v>646.3009188</v>
       </c>
       <c r="N75">
-        <v>-405.6421226000001</v>
+        <v>-414.3759188</v>
       </c>
       <c r="O75">
-        <v>-89.24126697200002</v>
+        <v>-91.16270213600001</v>
       </c>
       <c r="P75">
-        <v>-316.4008556280001</v>
+        <v>-323.213216664</v>
       </c>
       <c r="Q75">
-        <v>-256.2008556280001</v>
+        <v>-263.013216664</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2004662722956291</v>
+        <v>0.2064149750762302</v>
       </c>
       <c r="T75">
-        <v>2.015820015982784</v>
+        <v>2.093351555059045</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.0800284365227712</v>
+        <v>0.07894697116435538</v>
       </c>
       <c r="W75">
-        <v>0.2169292946679305</v>
+        <v>0.217184304199445</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.363765620558051</v>
+        <v>0.3588498689288881</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2143842786274092</v>
+        <v>0.2162842786274092</v>
       </c>
       <c r="C76">
-        <v>-1734.831540528626</v>
+        <v>-1783.082738441451</v>
       </c>
       <c r="D76">
-        <v>1006.054459471374</v>
+        <v>994.8422615585491</v>
       </c>
       <c r="E76">
-        <v>1466.786</v>
+        <v>1503.825</v>
       </c>
       <c r="F76">
-        <v>2740.886</v>
+        <v>2777.925</v>
       </c>
       <c r="G76">
         <v>0</v>
@@ -7519,37 +7519,37 @@
         <v>231.925</v>
       </c>
       <c r="M76">
-        <v>646.3009188</v>
+        <v>655.0347150000001</v>
       </c>
       <c r="N76">
-        <v>-414.3759188</v>
+        <v>-423.1097150000002</v>
       </c>
       <c r="O76">
-        <v>-91.16270213600001</v>
+        <v>-93.08413730000004</v>
       </c>
       <c r="P76">
-        <v>-323.213216664</v>
+        <v>-330.0255777000001</v>
       </c>
       <c r="Q76">
-        <v>-263.013216664</v>
+        <v>-269.8255777000001</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2064149750762302</v>
+        <v>0.2128395740792794</v>
       </c>
       <c r="T76">
-        <v>2.093351555059045</v>
+        <v>2.177085617261407</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.07894697116435538</v>
+        <v>0.07789434488216397</v>
       </c>
       <c r="W76">
-        <v>0.217184304199445</v>
+        <v>0.2174325134767857</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3588498689288881</v>
+        <v>0.3540652040098362</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2162842786274092</v>
+        <v>0.2181842786274092</v>
       </c>
       <c r="C77">
-        <v>-1783.082738441451</v>
+        <v>-1831.086777202594</v>
       </c>
       <c r="D77">
-        <v>994.8422615585491</v>
+        <v>983.8772227974064</v>
       </c>
       <c r="E77">
-        <v>1503.825</v>
+        <v>1540.864</v>
       </c>
       <c r="F77">
-        <v>2777.925</v>
+        <v>2814.964</v>
       </c>
       <c r="G77">
         <v>0</v>
@@ -7601,37 +7601,37 @@
         <v>231.925</v>
       </c>
       <c r="M77">
-        <v>655.0347150000001</v>
+        <v>663.7685112</v>
       </c>
       <c r="N77">
-        <v>-423.1097150000002</v>
+        <v>-431.8435112000001</v>
       </c>
       <c r="O77">
-        <v>-93.08413730000004</v>
+        <v>-95.00557246400002</v>
       </c>
       <c r="P77">
-        <v>-330.0255777000001</v>
+        <v>-336.8379387360001</v>
       </c>
       <c r="Q77">
-        <v>-269.8255777000001</v>
+        <v>-276.6379387360001</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2128395740792794</v>
+        <v>0.2197995563325827</v>
       </c>
       <c r="T77">
-        <v>2.177085617261407</v>
+        <v>2.267797517980632</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.07789434488216397</v>
+        <v>0.07686941929160919</v>
       </c>
       <c r="W77">
-        <v>0.2174325134767857</v>
+        <v>0.2176741909310386</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3540652040098362</v>
+        <v>0.3494064513254963</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2181842786274092</v>
+        <v>0.2200842786274091</v>
       </c>
       <c r="C78">
-        <v>-1831.086777202594</v>
+        <v>-1878.851740198439</v>
       </c>
       <c r="D78">
-        <v>983.8772227974064</v>
+        <v>973.151259801561</v>
       </c>
       <c r="E78">
-        <v>1540.864</v>
+        <v>1577.903</v>
       </c>
       <c r="F78">
-        <v>2814.964</v>
+        <v>2852.003</v>
       </c>
       <c r="G78">
         <v>0</v>
@@ -7683,37 +7683,37 @@
         <v>231.925</v>
       </c>
       <c r="M78">
-        <v>663.7685112</v>
+        <v>672.5023074000001</v>
       </c>
       <c r="N78">
-        <v>-431.8435112000001</v>
+        <v>-440.5773074000001</v>
       </c>
       <c r="O78">
-        <v>-95.00557246400002</v>
+        <v>-96.92700762800003</v>
       </c>
       <c r="P78">
-        <v>-336.8379387360001</v>
+        <v>-343.6502997720001</v>
       </c>
       <c r="Q78">
-        <v>-276.6379387360001</v>
+        <v>-283.4502997720001</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2197995563325827</v>
+        <v>0.2273647544339994</v>
       </c>
       <c r="T78">
-        <v>2.267797517980632</v>
+        <v>2.366397410066746</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.07686941929160919</v>
+        <v>0.0758711151449649</v>
       </c>
       <c r="W78">
-        <v>0.2176741909310386</v>
+        <v>0.2179095910488173</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3494064513254963</v>
+        <v>0.344868705204386</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2200842786274091</v>
+        <v>0.2219842786274092</v>
       </c>
       <c r="C79">
-        <v>-1878.851740198439</v>
+        <v>-1926.385362125139</v>
       </c>
       <c r="D79">
-        <v>973.151259801561</v>
+        <v>962.6566378748614</v>
       </c>
       <c r="E79">
-        <v>1577.903</v>
+        <v>1614.942</v>
       </c>
       <c r="F79">
-        <v>2852.003</v>
+        <v>2889.042</v>
       </c>
       <c r="G79">
         <v>0</v>
@@ -7765,37 +7765,37 @@
         <v>231.925</v>
       </c>
       <c r="M79">
-        <v>672.5023074000001</v>
+        <v>681.2361036000001</v>
       </c>
       <c r="N79">
-        <v>-440.5773074000001</v>
+        <v>-449.3111036000001</v>
       </c>
       <c r="O79">
-        <v>-96.92700762800003</v>
+        <v>-98.84844279200003</v>
       </c>
       <c r="P79">
-        <v>-343.6502997720001</v>
+        <v>-350.4626608080001</v>
       </c>
       <c r="Q79">
-        <v>-283.4502997720001</v>
+        <v>-290.2626608080001</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2273647544339994</v>
+        <v>0.235617697817363</v>
       </c>
       <c r="T79">
-        <v>2.366397410066746</v>
+        <v>2.473960928706144</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.0758711151449649</v>
+        <v>0.07489840854054228</v>
       </c>
       <c r="W79">
-        <v>0.2179095910488173</v>
+        <v>0.2181389552661401</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.344868705204386</v>
+        <v>0.3404473115479194</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2219842786274092</v>
+        <v>0.2238842786274092</v>
       </c>
       <c r="C80">
-        <v>-1926.385362125139</v>
+        <v>-1973.695047589682</v>
       </c>
       <c r="D80">
-        <v>962.6566378748614</v>
+        <v>952.3859524103179</v>
       </c>
       <c r="E80">
-        <v>1614.942</v>
+        <v>1651.981</v>
       </c>
       <c r="F80">
-        <v>2889.042</v>
+        <v>2926.081</v>
       </c>
       <c r="G80">
         <v>0</v>
@@ -7847,37 +7847,37 @@
         <v>231.925</v>
       </c>
       <c r="M80">
-        <v>681.2361036000001</v>
+        <v>689.9698998</v>
       </c>
       <c r="N80">
-        <v>-449.3111036000001</v>
+        <v>-458.0448998000001</v>
       </c>
       <c r="O80">
-        <v>-98.84844279200003</v>
+        <v>-100.769877956</v>
       </c>
       <c r="P80">
-        <v>-350.4626608080001</v>
+        <v>-357.275021844</v>
       </c>
       <c r="Q80">
-        <v>-290.2626608080001</v>
+        <v>-297.075021844</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.235617697817363</v>
+        <v>0.244656635808666</v>
       </c>
       <c r="T80">
-        <v>2.473960928706144</v>
+        <v>2.591768591977865</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.07489840854054228</v>
+        <v>0.07395032741977592</v>
       </c>
       <c r="W80">
-        <v>0.2181389552661401</v>
+        <v>0.2183625127944168</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3404473115479194</v>
+        <v>0.3361378519080724</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2238842786274092</v>
+        <v>0.2257842786274092</v>
       </c>
       <c r="C81">
-        <v>-1973.695047589682</v>
+        <v>-2020.787888532788</v>
       </c>
       <c r="D81">
-        <v>952.3859524103179</v>
+        <v>942.3321114672119</v>
       </c>
       <c r="E81">
-        <v>1651.981</v>
+        <v>1689.02</v>
       </c>
       <c r="F81">
-        <v>2926.081</v>
+        <v>2963.12</v>
       </c>
       <c r="G81">
         <v>0</v>
@@ -7929,37 +7929,37 @@
         <v>231.925</v>
       </c>
       <c r="M81">
-        <v>689.9698998</v>
+        <v>698.7036960000001</v>
       </c>
       <c r="N81">
-        <v>-458.0448998000001</v>
+        <v>-466.7786960000002</v>
       </c>
       <c r="O81">
-        <v>-100.769877956</v>
+        <v>-102.69131312</v>
       </c>
       <c r="P81">
-        <v>-357.275021844</v>
+        <v>-364.0873828800002</v>
       </c>
       <c r="Q81">
-        <v>-297.075021844</v>
+        <v>-303.8873828800002</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.244656635808666</v>
+        <v>0.2545994675990993</v>
       </c>
       <c r="T81">
-        <v>2.591768591977865</v>
+        <v>2.721357021576759</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.07395032741977592</v>
+        <v>0.0730259483270287</v>
       </c>
       <c r="W81">
-        <v>0.2183625127944168</v>
+        <v>0.2185804813844867</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3361378519080724</v>
+        <v>0.3319361287592214</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2257842786274092</v>
+        <v>0.2276842786274091</v>
       </c>
       <c r="C82">
-        <v>-2020.787888532788</v>
+        <v>-2067.67068055978</v>
       </c>
       <c r="D82">
-        <v>942.3321114672119</v>
+        <v>932.4883194402203</v>
       </c>
       <c r="E82">
-        <v>1689.02</v>
+        <v>1726.059</v>
       </c>
       <c r="F82">
-        <v>2963.12</v>
+        <v>3000.159</v>
       </c>
       <c r="G82">
         <v>0</v>
@@ -8011,37 +8011,37 @@
         <v>231.925</v>
       </c>
       <c r="M82">
-        <v>698.7036960000001</v>
+        <v>707.4374922000001</v>
       </c>
       <c r="N82">
-        <v>-466.7786960000002</v>
+        <v>-475.5124922000001</v>
       </c>
       <c r="O82">
-        <v>-102.69131312</v>
+        <v>-104.612748284</v>
       </c>
       <c r="P82">
-        <v>-364.0873828800002</v>
+        <v>-370.8997439160001</v>
       </c>
       <c r="Q82">
-        <v>-303.8873828800002</v>
+        <v>-310.6997439160001</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2545994675990993</v>
+        <v>0.2655889132622098</v>
       </c>
       <c r="T82">
-        <v>2.721357021576759</v>
+        <v>2.864586338501852</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.0730259483270287</v>
+        <v>0.07212439340941108</v>
       </c>
       <c r="W82">
-        <v>0.2185804813844867</v>
+        <v>0.2187930680340609</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3319361287592214</v>
+        <v>0.3278381518609594</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2276842786274091</v>
+        <v>0.2295842786274092</v>
       </c>
       <c r="C83">
-        <v>-2067.67068055978</v>
+        <v>-2114.349938258472</v>
       </c>
       <c r="D83">
-        <v>932.4883194402203</v>
+        <v>922.8480617415282</v>
       </c>
       <c r="E83">
-        <v>1726.059</v>
+        <v>1763.098</v>
       </c>
       <c r="F83">
-        <v>3000.159</v>
+        <v>3037.198</v>
       </c>
       <c r="G83">
         <v>0</v>
@@ -8093,37 +8093,37 @@
         <v>231.925</v>
       </c>
       <c r="M83">
-        <v>707.4374922000001</v>
+        <v>716.1712884000001</v>
       </c>
       <c r="N83">
-        <v>-475.5124922000001</v>
+        <v>-484.2462884000001</v>
       </c>
       <c r="O83">
-        <v>-104.612748284</v>
+        <v>-106.534183448</v>
       </c>
       <c r="P83">
-        <v>-370.8997439160001</v>
+        <v>-377.7121049520001</v>
       </c>
       <c r="Q83">
-        <v>-310.6997439160001</v>
+        <v>-317.5121049520001</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2655889132622098</v>
+        <v>0.2777994084434437</v>
       </c>
       <c r="T83">
-        <v>2.864586338501852</v>
+        <v>3.023730023974177</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.07212439340941108</v>
+        <v>0.07124482763612558</v>
       </c>
       <c r="W83">
-        <v>0.2187930680340609</v>
+        <v>0.2190004696434016</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3278381518609594</v>
+        <v>0.3238401256187526</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2295842786274092</v>
+        <v>0.2314842786274092</v>
       </c>
       <c r="C84">
-        <v>-2114.349938258472</v>
+        <v>-2160.831909576616</v>
       </c>
       <c r="D84">
-        <v>922.8480617415282</v>
+        <v>913.405090423384</v>
       </c>
       <c r="E84">
-        <v>1763.098</v>
+        <v>1800.137000000001</v>
       </c>
       <c r="F84">
-        <v>3037.198</v>
+        <v>3074.237000000001</v>
       </c>
       <c r="G84">
         <v>0</v>
@@ -8175,37 +8175,37 @@
         <v>231.925</v>
       </c>
       <c r="M84">
-        <v>716.1712884000001</v>
+        <v>724.9050846000001</v>
       </c>
       <c r="N84">
-        <v>-484.2462884000001</v>
+        <v>-492.9800846000002</v>
       </c>
       <c r="O84">
-        <v>-106.534183448</v>
+        <v>-108.455618612</v>
       </c>
       <c r="P84">
-        <v>-377.7121049520001</v>
+        <v>-384.5244659880001</v>
       </c>
       <c r="Q84">
-        <v>-317.5121049520001</v>
+        <v>-324.3244659880002</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2777994084434437</v>
+        <v>0.2914464324695286</v>
       </c>
       <c r="T84">
-        <v>3.023730023974177</v>
+        <v>3.201596495972658</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.07124482763612558</v>
+        <v>0.07038645621882286</v>
       </c>
       <c r="W84">
-        <v>0.2190004696434016</v>
+        <v>0.2192028736236016</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3238401256187526</v>
+        <v>0.3199384373582858</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2314842786274092</v>
+        <v>0.2333842786274092</v>
       </c>
       <c r="C85">
-        <v>-2160.831909576616</v>
+        <v>-2207.122589325598</v>
       </c>
       <c r="D85">
-        <v>913.405090423384</v>
+        <v>904.1534106744026</v>
       </c>
       <c r="E85">
-        <v>1800.137000000001</v>
+        <v>1837.176</v>
       </c>
       <c r="F85">
-        <v>3074.237000000001</v>
+        <v>3111.276</v>
       </c>
       <c r="G85">
         <v>0</v>
@@ -8257,37 +8257,37 @@
         <v>231.925</v>
       </c>
       <c r="M85">
-        <v>724.9050846000001</v>
+        <v>733.6388808000002</v>
       </c>
       <c r="N85">
-        <v>-492.9800846000002</v>
+        <v>-501.7138808000002</v>
       </c>
       <c r="O85">
-        <v>-108.455618612</v>
+        <v>-110.377053776</v>
       </c>
       <c r="P85">
-        <v>-384.5244659880001</v>
+        <v>-391.3368270240002</v>
       </c>
       <c r="Q85">
-        <v>-324.3244659880002</v>
+        <v>-331.1368270240002</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2914464324695286</v>
+        <v>0.3067993344988743</v>
       </c>
       <c r="T85">
-        <v>3.201596495972658</v>
+        <v>3.40169627697095</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.07038645621882286</v>
+        <v>0.06954852221621782</v>
       </c>
       <c r="W85">
-        <v>0.2192028736236016</v>
+        <v>0.2194004584614159</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3199384373582858</v>
+        <v>0.3161296464373538</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2333842786274092</v>
+        <v>0.2352842786274092</v>
       </c>
       <c r="C86">
-        <v>-2207.122589325596</v>
+        <v>-2253.227731871698</v>
       </c>
       <c r="D86">
-        <v>904.1534106744034</v>
+        <v>895.0872681283017</v>
       </c>
       <c r="E86">
-        <v>1837.176</v>
+        <v>1874.215</v>
       </c>
       <c r="F86">
-        <v>3111.276</v>
+        <v>3148.315</v>
       </c>
       <c r="G86">
         <v>0</v>
@@ -8339,37 +8339,37 @@
         <v>231.925</v>
       </c>
       <c r="M86">
-        <v>733.6388808</v>
+        <v>742.3726770000001</v>
       </c>
       <c r="N86">
-        <v>-501.7138808000001</v>
+        <v>-510.4476770000001</v>
       </c>
       <c r="O86">
-        <v>-110.377053776</v>
+        <v>-112.29848894</v>
       </c>
       <c r="P86">
-        <v>-391.3368270240001</v>
+        <v>-398.1491880600001</v>
       </c>
       <c r="Q86">
-        <v>-331.1368270240001</v>
+        <v>-337.9491880600001</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.306799334498874</v>
+        <v>0.3241992901321323</v>
       </c>
       <c r="T86">
-        <v>3.401696276970947</v>
+        <v>3.628476028769011</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.06954852221621784</v>
+        <v>0.06873030430779174</v>
       </c>
       <c r="W86">
-        <v>0.2194004584614158</v>
+        <v>0.2195933942442227</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3161296464373538</v>
+        <v>0.3124104741263261</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2352842786274092</v>
+        <v>0.2371842786274092</v>
       </c>
       <c r="C87">
-        <v>-2253.227731871698</v>
+        <v>-2299.152863071402</v>
       </c>
       <c r="D87">
-        <v>895.0872681283017</v>
+        <v>886.2011369285976</v>
       </c>
       <c r="E87">
-        <v>1874.215</v>
+        <v>1911.254</v>
       </c>
       <c r="F87">
-        <v>3148.315</v>
+        <v>3185.354</v>
       </c>
       <c r="G87">
         <v>0</v>
@@ -8421,37 +8421,37 @@
         <v>231.925</v>
       </c>
       <c r="M87">
-        <v>742.3726770000001</v>
+        <v>751.1064732</v>
       </c>
       <c r="N87">
-        <v>-510.4476770000001</v>
+        <v>-519.1814732</v>
       </c>
       <c r="O87">
-        <v>-112.29848894</v>
+        <v>-114.219924104</v>
       </c>
       <c r="P87">
-        <v>-398.1491880600001</v>
+        <v>-404.961549096</v>
       </c>
       <c r="Q87">
-        <v>-337.9491880600001</v>
+        <v>-344.761549096</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3241992901321323</v>
+        <v>0.344084953712999</v>
       </c>
       <c r="T87">
-        <v>3.628476028769011</v>
+        <v>3.887652887966798</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.06873030430779174</v>
+        <v>0.06793111472281742</v>
       </c>
       <c r="W87">
-        <v>0.2195933942442227</v>
+        <v>0.2197818431483597</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3124104741263261</v>
+        <v>0.3087777941946247</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2371842786274092</v>
+        <v>0.2390842786274092</v>
       </c>
       <c r="C88">
-        <v>-2299.152863071402</v>
+        <v>-2344.903291502735</v>
       </c>
       <c r="D88">
-        <v>886.2011369285976</v>
+        <v>877.4897084972653</v>
       </c>
       <c r="E88">
-        <v>1911.254</v>
+        <v>1948.293</v>
       </c>
       <c r="F88">
-        <v>3185.354</v>
+        <v>3222.393</v>
       </c>
       <c r="G88">
         <v>0</v>
@@ -8503,37 +8503,37 @@
         <v>231.925</v>
       </c>
       <c r="M88">
-        <v>751.1064732</v>
+        <v>759.8402694</v>
       </c>
       <c r="N88">
-        <v>-519.1814732</v>
+        <v>-527.9152694000001</v>
       </c>
       <c r="O88">
-        <v>-114.219924104</v>
+        <v>-116.141359268</v>
       </c>
       <c r="P88">
-        <v>-404.961549096</v>
+        <v>-411.773910132</v>
       </c>
       <c r="Q88">
-        <v>-344.761549096</v>
+        <v>-351.573910132</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.344084953712999</v>
+        <v>0.3670299501524604</v>
       </c>
       <c r="T88">
-        <v>3.887652887966798</v>
+        <v>4.186703110118089</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.06793111472281742</v>
+        <v>0.06715029731221032</v>
       </c>
       <c r="W88">
-        <v>0.2197818431483597</v>
+        <v>0.2199659598937808</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3087777941946247</v>
+        <v>0.3052286241464106</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2390842786274092</v>
+        <v>0.2409842786274091</v>
       </c>
       <c r="C89">
-        <v>-2344.903291502735</v>
+        <v>-2390.484119040634</v>
       </c>
       <c r="D89">
-        <v>877.4897084972653</v>
+        <v>868.947880959366</v>
       </c>
       <c r="E89">
-        <v>1948.293</v>
+        <v>1985.332</v>
       </c>
       <c r="F89">
-        <v>3222.393</v>
+        <v>3259.432</v>
       </c>
       <c r="G89">
         <v>0</v>
@@ -8585,37 +8585,37 @@
         <v>231.925</v>
       </c>
       <c r="M89">
-        <v>759.8402694</v>
+        <v>768.5740656</v>
       </c>
       <c r="N89">
-        <v>-527.9152694000001</v>
+        <v>-536.6490656000001</v>
       </c>
       <c r="O89">
-        <v>-116.141359268</v>
+        <v>-118.062794432</v>
       </c>
       <c r="P89">
-        <v>-411.773910132</v>
+        <v>-418.5862711680001</v>
       </c>
       <c r="Q89">
-        <v>-351.573910132</v>
+        <v>-358.3862711680001</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3670299501524604</v>
+        <v>0.3937991126651655</v>
       </c>
       <c r="T89">
-        <v>4.186703110118089</v>
+        <v>4.535595035961264</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.06715029731221032</v>
+        <v>0.06638722575184429</v>
       </c>
       <c r="W89">
-        <v>0.2199659598937808</v>
+        <v>0.2201458921677151</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3052286241464106</v>
+        <v>0.3017601170538378</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2409842786274091</v>
+        <v>0.2428842786274092</v>
       </c>
       <c r="C90">
-        <v>-2390.484119040634</v>
+        <v>-2435.900250820608</v>
       </c>
       <c r="D90">
-        <v>868.947880959366</v>
+        <v>860.5707491793924</v>
       </c>
       <c r="E90">
-        <v>1985.332</v>
+        <v>2022.371</v>
       </c>
       <c r="F90">
-        <v>3259.432</v>
+        <v>3296.471</v>
       </c>
       <c r="G90">
         <v>0</v>
@@ -8667,37 +8667,37 @@
         <v>231.925</v>
       </c>
       <c r="M90">
-        <v>768.5740656</v>
+        <v>777.3078618000001</v>
       </c>
       <c r="N90">
-        <v>-536.6490656000001</v>
+        <v>-545.3828618000001</v>
       </c>
       <c r="O90">
-        <v>-118.062794432</v>
+        <v>-119.984229596</v>
       </c>
       <c r="P90">
-        <v>-418.5862711680001</v>
+        <v>-425.3986322040001</v>
       </c>
       <c r="Q90">
-        <v>-358.3862711680001</v>
+        <v>-365.1986322040001</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3937991126651655</v>
+        <v>0.425435395634726</v>
       </c>
       <c r="T90">
-        <v>4.535595035961264</v>
+        <v>4.947921857412289</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.06638722575184429</v>
+        <v>0.06564130186699212</v>
       </c>
       <c r="W90">
-        <v>0.2201458921677151</v>
+        <v>0.2203217810197633</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3017601170538378</v>
+        <v>0.2983695539408733</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2428842786274092</v>
+        <v>0.2447842786274091</v>
       </c>
       <c r="C91">
-        <v>-2435.900250820608</v>
+        <v>-2481.156404631551</v>
       </c>
       <c r="D91">
-        <v>860.5707491793924</v>
+        <v>852.3535953684495</v>
       </c>
       <c r="E91">
-        <v>2022.371</v>
+        <v>2059.41</v>
       </c>
       <c r="F91">
-        <v>3296.471</v>
+        <v>3333.51</v>
       </c>
       <c r="G91">
         <v>0</v>
@@ -8749,37 +8749,37 @@
         <v>231.925</v>
       </c>
       <c r="M91">
-        <v>777.3078618000001</v>
+        <v>786.0416580000001</v>
       </c>
       <c r="N91">
-        <v>-545.3828618000001</v>
+        <v>-554.1166580000001</v>
       </c>
       <c r="O91">
-        <v>-119.984229596</v>
+        <v>-121.90566476</v>
       </c>
       <c r="P91">
-        <v>-425.3986322040001</v>
+        <v>-432.2109932400001</v>
       </c>
       <c r="Q91">
-        <v>-365.1986322040001</v>
+        <v>-372.0109932400001</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.425435395634726</v>
+        <v>0.4633989351981986</v>
       </c>
       <c r="T91">
-        <v>4.947921857412289</v>
+        <v>5.442714043153518</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.06564130186699212</v>
+        <v>0.06491195406846997</v>
       </c>
       <c r="W91">
-        <v>0.2203217810197633</v>
+        <v>0.2204937612306548</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2983695539408733</v>
+        <v>0.2950543366748635</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2447842786274091</v>
+        <v>0.2466842786274092</v>
       </c>
       <c r="C92">
-        <v>-2481.156404631551</v>
+        <v>-2526.25711977554</v>
       </c>
       <c r="D92">
-        <v>852.3535953684495</v>
+        <v>844.29188022446</v>
       </c>
       <c r="E92">
-        <v>2059.41</v>
+        <v>2096.449</v>
       </c>
       <c r="F92">
-        <v>3333.51</v>
+        <v>3370.549</v>
       </c>
       <c r="G92">
         <v>0</v>
@@ -8831,37 +8831,37 @@
         <v>231.925</v>
       </c>
       <c r="M92">
-        <v>786.0416580000001</v>
+        <v>794.7754542</v>
       </c>
       <c r="N92">
-        <v>-554.1166580000001</v>
+        <v>-562.8504542000001</v>
       </c>
       <c r="O92">
-        <v>-121.90566476</v>
+        <v>-123.827099924</v>
       </c>
       <c r="P92">
-        <v>-432.2109932400001</v>
+        <v>-439.0233542760001</v>
       </c>
       <c r="Q92">
-        <v>-372.0109932400001</v>
+        <v>-378.8233542760001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4633989351981986</v>
+        <v>0.5097988168868874</v>
       </c>
       <c r="T92">
-        <v>5.442714043153518</v>
+        <v>6.047460047948354</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.06491195406846997</v>
+        <v>0.0641986358918934</v>
       </c>
       <c r="W92">
-        <v>0.2204937612306548</v>
+        <v>0.2206619616566916</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2950543366748635</v>
+        <v>0.2918119813267881</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2466842786274092</v>
+        <v>0.2485842786274092</v>
       </c>
       <c r="C93">
-        <v>-2526.25711977554</v>
+        <v>-2571.206765429555</v>
       </c>
       <c r="D93">
-        <v>844.29188022446</v>
+        <v>836.3812345704448</v>
       </c>
       <c r="E93">
-        <v>2096.449</v>
+        <v>2133.488</v>
       </c>
       <c r="F93">
-        <v>3370.549</v>
+        <v>3407.588</v>
       </c>
       <c r="G93">
         <v>0</v>
@@ -8913,37 +8913,37 @@
         <v>231.925</v>
       </c>
       <c r="M93">
-        <v>794.7754542</v>
+        <v>803.5092504</v>
       </c>
       <c r="N93">
-        <v>-562.8504542000001</v>
+        <v>-571.5842504000001</v>
       </c>
       <c r="O93">
-        <v>-123.827099924</v>
+        <v>-125.748535088</v>
       </c>
       <c r="P93">
-        <v>-439.0233542760001</v>
+        <v>-445.835715312</v>
       </c>
       <c r="Q93">
-        <v>-378.8233542760001</v>
+        <v>-385.6357153120001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5097988168868874</v>
+        <v>0.5677986689977484</v>
       </c>
       <c r="T93">
-        <v>6.047460047948354</v>
+        <v>6.8033925539419</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.0641986358918934</v>
+        <v>0.06350082463219889</v>
       </c>
       <c r="W93">
-        <v>0.2206619616566916</v>
+        <v>0.2208265055517275</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2918119813267881</v>
+        <v>0.2886401119645404</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2485842786274092</v>
+        <v>0.2504842786274092</v>
       </c>
       <c r="C94">
-        <v>-2571.206765429555</v>
+        <v>-2616.00954854148</v>
       </c>
       <c r="D94">
-        <v>836.3812345704448</v>
+        <v>828.6174514585203</v>
       </c>
       <c r="E94">
-        <v>2133.488</v>
+        <v>2170.527</v>
       </c>
       <c r="F94">
-        <v>3407.588</v>
+        <v>3444.627</v>
       </c>
       <c r="G94">
         <v>0</v>
@@ -8995,37 +8995,37 @@
         <v>231.925</v>
       </c>
       <c r="M94">
-        <v>803.5092504</v>
+        <v>812.2430466000002</v>
       </c>
       <c r="N94">
-        <v>-571.5842504000001</v>
+        <v>-580.3180466000002</v>
       </c>
       <c r="O94">
-        <v>-125.748535088</v>
+        <v>-127.6699702520001</v>
       </c>
       <c r="P94">
-        <v>-445.835715312</v>
+        <v>-452.6480763480002</v>
       </c>
       <c r="Q94">
-        <v>-385.6357153120001</v>
+        <v>-392.4480763480002</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5677986689977484</v>
+        <v>0.6423699074259983</v>
       </c>
       <c r="T94">
-        <v>6.8033925539419</v>
+        <v>7.775305775933601</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.06350082463219889</v>
+        <v>0.06281802006626126</v>
       </c>
       <c r="W94">
-        <v>0.2208265055517275</v>
+        <v>0.2209875108683756</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2886401119645404</v>
+        <v>0.285536454846642</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2504842786274092</v>
+        <v>0.2523842786274092</v>
       </c>
       <c r="C95">
-        <v>-2616.00954854148</v>
+        <v>-2660.669521290382</v>
       </c>
       <c r="D95">
-        <v>828.6174514585203</v>
+        <v>820.9964787096177</v>
       </c>
       <c r="E95">
-        <v>2170.527</v>
+        <v>2207.566</v>
       </c>
       <c r="F95">
-        <v>3444.627</v>
+        <v>3481.666</v>
       </c>
       <c r="G95">
         <v>0</v>
@@ -9077,37 +9077,37 @@
         <v>231.925</v>
       </c>
       <c r="M95">
-        <v>812.2430466000002</v>
+        <v>820.9768428000001</v>
       </c>
       <c r="N95">
-        <v>-580.3180466000002</v>
+        <v>-589.0518428000001</v>
       </c>
       <c r="O95">
-        <v>-127.6699702520001</v>
+        <v>-129.591405416</v>
       </c>
       <c r="P95">
-        <v>-452.6480763480002</v>
+        <v>-459.4604373840001</v>
       </c>
       <c r="Q95">
-        <v>-392.4480763480002</v>
+        <v>-399.2604373840001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6423699074259983</v>
+        <v>0.7417982253303316</v>
       </c>
       <c r="T95">
-        <v>7.775305775933601</v>
+        <v>9.071190071922537</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.06281802006626126</v>
+        <v>0.06214974325704573</v>
       </c>
       <c r="W95">
-        <v>0.2209875108683756</v>
+        <v>0.2211450905399886</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.285536454846642</v>
+        <v>0.2824988329865714</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2523842786274092</v>
+        <v>0.2542842786274092</v>
       </c>
       <c r="C96">
-        <v>-2660.669521290382</v>
+        <v>-2705.190588138867</v>
       </c>
       <c r="D96">
-        <v>820.9964787096177</v>
+        <v>813.5144118611335</v>
       </c>
       <c r="E96">
-        <v>2207.566</v>
+        <v>2244.605</v>
       </c>
       <c r="F96">
-        <v>3481.666</v>
+        <v>3518.705</v>
       </c>
       <c r="G96">
         <v>0</v>
@@ -9159,37 +9159,37 @@
         <v>231.925</v>
       </c>
       <c r="M96">
-        <v>820.9768428000001</v>
+        <v>829.7106390000001</v>
       </c>
       <c r="N96">
-        <v>-589.0518428000001</v>
+        <v>-597.7856390000002</v>
       </c>
       <c r="O96">
-        <v>-129.591405416</v>
+        <v>-131.51284058</v>
       </c>
       <c r="P96">
-        <v>-459.4604373840001</v>
+        <v>-466.2727984200001</v>
       </c>
       <c r="Q96">
-        <v>-399.2604373840001</v>
+        <v>-406.0727984200001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.7417982253303316</v>
+        <v>0.8809978703963983</v>
       </c>
       <c r="T96">
-        <v>9.071190071922537</v>
+        <v>10.88542808630705</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.06214974325704573</v>
+        <v>0.06149553543328734</v>
       </c>
       <c r="W96">
-        <v>0.2211450905399886</v>
+        <v>0.2212993527448308</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2824988329865714</v>
+        <v>0.279525161060397</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2542842786274092</v>
+        <v>0.2561842786274092</v>
       </c>
       <c r="C97">
-        <v>-2705.190588138867</v>
+        <v>-2749.576512503275</v>
       </c>
       <c r="D97">
-        <v>813.5144118611335</v>
+        <v>806.1674874967255</v>
       </c>
       <c r="E97">
-        <v>2244.605</v>
+        <v>2281.644</v>
       </c>
       <c r="F97">
-        <v>3518.705</v>
+        <v>3555.744</v>
       </c>
       <c r="G97">
         <v>0</v>
@@ -9241,37 +9241,37 @@
         <v>231.925</v>
       </c>
       <c r="M97">
-        <v>829.7106390000001</v>
+        <v>838.4444352</v>
       </c>
       <c r="N97">
-        <v>-597.7856390000002</v>
+        <v>-606.5194352000001</v>
       </c>
       <c r="O97">
-        <v>-131.51284058</v>
+        <v>-133.434275744</v>
       </c>
       <c r="P97">
-        <v>-466.2727984200001</v>
+        <v>-473.085159456</v>
       </c>
       <c r="Q97">
-        <v>-406.0727984200001</v>
+        <v>-412.8851594560001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.8809978703963983</v>
+        <v>1.089797337995498</v>
       </c>
       <c r="T97">
-        <v>10.88542808630705</v>
+        <v>13.60678510788382</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.06149553543328734</v>
+        <v>0.0608549569391906</v>
       </c>
       <c r="W97">
-        <v>0.2212993527448308</v>
+        <v>0.2214504011537388</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.279525161060397</v>
+        <v>0.2766134406326846</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2561842786274092</v>
+        <v>0.2580842786274092</v>
       </c>
       <c r="C98">
-        <v>-2749.576512503275</v>
+        <v>-2793.830923065694</v>
       </c>
       <c r="D98">
-        <v>806.1674874967255</v>
+        <v>798.952076934306</v>
       </c>
       <c r="E98">
-        <v>2281.644</v>
+        <v>2318.683</v>
       </c>
       <c r="F98">
-        <v>3555.744</v>
+        <v>3592.783</v>
       </c>
       <c r="G98">
         <v>0</v>
@@ -9323,37 +9323,37 @@
         <v>231.925</v>
       </c>
       <c r="M98">
-        <v>838.4444352</v>
+        <v>847.1782314</v>
       </c>
       <c r="N98">
-        <v>-606.5194352000001</v>
+        <v>-615.2532314</v>
       </c>
       <c r="O98">
-        <v>-133.434275744</v>
+        <v>-135.355710908</v>
       </c>
       <c r="P98">
-        <v>-473.085159456</v>
+        <v>-479.897520492</v>
       </c>
       <c r="Q98">
-        <v>-412.8851594560001</v>
+        <v>-419.697520492</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.089797337995495</v>
+        <v>1.437796450660661</v>
       </c>
       <c r="T98">
-        <v>13.60678510788378</v>
+        <v>18.14238014384504</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.0608549569391906</v>
+        <v>0.06022758624909585</v>
       </c>
       <c r="W98">
-        <v>0.2214504011537388</v>
+        <v>0.2215983351624632</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2766134406326846</v>
+        <v>0.2737617556777084</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2580842786274092</v>
+        <v>0.2599842786274092</v>
       </c>
       <c r="C99">
-        <v>-2793.830923065694</v>
+        <v>-2837.957319750004</v>
       </c>
       <c r="D99">
-        <v>798.952076934306</v>
+        <v>791.8646802499964</v>
       </c>
       <c r="E99">
-        <v>2318.683</v>
+        <v>2355.722</v>
       </c>
       <c r="F99">
-        <v>3592.783</v>
+        <v>3629.822</v>
       </c>
       <c r="G99">
         <v>0</v>
@@ -9405,37 +9405,37 @@
         <v>231.925</v>
       </c>
       <c r="M99">
-        <v>847.1782314</v>
+        <v>855.9120276000001</v>
       </c>
       <c r="N99">
-        <v>-615.2532314</v>
+        <v>-623.9870276000001</v>
       </c>
       <c r="O99">
-        <v>-135.355710908</v>
+        <v>-137.277146072</v>
       </c>
       <c r="P99">
-        <v>-479.897520492</v>
+        <v>-486.7098815280001</v>
       </c>
       <c r="Q99">
-        <v>-419.697520492</v>
+        <v>-426.5098815280001</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.437796450660661</v>
+        <v>2.133794675990991</v>
       </c>
       <c r="T99">
-        <v>18.14238014384504</v>
+        <v>27.21357021576756</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.06022758624909585</v>
+        <v>0.05961301904247242</v>
       </c>
       <c r="W99">
-        <v>0.2215983351624632</v>
+        <v>0.221743250109785</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2737617556777084</v>
+        <v>0.2709682683748746</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2599842786274092</v>
+        <v>0.2618842786274092</v>
       </c>
       <c r="C100">
-        <v>-2837.957319750004</v>
+        <v>-2881.959079382643</v>
       </c>
       <c r="D100">
-        <v>791.8646802499964</v>
+        <v>784.901920617357</v>
       </c>
       <c r="E100">
-        <v>2355.722</v>
+        <v>2392.761</v>
       </c>
       <c r="F100">
-        <v>3629.822</v>
+        <v>3666.861</v>
       </c>
       <c r="G100">
         <v>0</v>
@@ -9487,37 +9487,37 @@
         <v>231.925</v>
       </c>
       <c r="M100">
-        <v>855.9120276000001</v>
+        <v>864.6458238</v>
       </c>
       <c r="N100">
-        <v>-623.9870276000001</v>
+        <v>-632.7208238000001</v>
       </c>
       <c r="O100">
-        <v>-137.277146072</v>
+        <v>-139.198581236</v>
       </c>
       <c r="P100">
-        <v>-486.7098815280001</v>
+        <v>-493.5222425640001</v>
       </c>
       <c r="Q100">
-        <v>-426.5098815280001</v>
+        <v>-433.3222425640001</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.133794675990991</v>
+        <v>4.221789351981982</v>
       </c>
       <c r="T100">
-        <v>27.21357021576756</v>
+        <v>54.42714043153512</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.05961301904247242</v>
+        <v>0.05901086733497271</v>
       </c>
       <c r="W100">
-        <v>0.221743250109785</v>
+        <v>0.2218852374824134</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2709682683748746</v>
+        <v>0.2682312151589669</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2618842786274092</v>
-      </c>
-      <c r="C101">
-        <v>-2881.959079382643</v>
-      </c>
-      <c r="D101">
-        <v>784.901920617357</v>
-      </c>
-      <c r="E101">
-        <v>2392.761</v>
-      </c>
-      <c r="F101">
-        <v>3666.861</v>
-      </c>
-      <c r="G101">
-        <v>0</v>
-      </c>
-      <c r="H101">
-        <v>2429.8</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>292.1249999999999</v>
-      </c>
-      <c r="K101">
-        <v>60.19999999999999</v>
-      </c>
-      <c r="L101">
-        <v>231.925</v>
-      </c>
-      <c r="M101">
-        <v>864.6458238</v>
-      </c>
-      <c r="N101">
-        <v>-632.7208238000001</v>
-      </c>
-      <c r="O101">
-        <v>-139.198581236</v>
-      </c>
-      <c r="P101">
-        <v>-493.5222425640001</v>
-      </c>
-      <c r="Q101">
-        <v>-433.3222425640001</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.221789351981982</v>
-      </c>
-      <c r="T101">
-        <v>54.42714043153512</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.05901086733497271</v>
-      </c>
-      <c r="W101">
-        <v>0.2218852374824134</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2682312151589669</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
